--- a/tests/test_data/ОН_ФЭВТ_4 курс 2023 lite.xlsx
+++ b/tests/test_data/ОН_ФЭВТ_4 курс 2023 lite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\Work\YDev\EOS\vstu-xls\vstu_xls\tests\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C46C3C-E1EE-48BB-9B7C-C0744DFBB9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61DA73A-9EF9-4C13-BE3E-69FD0CE29B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5709" yWindow="0" windowWidth="19748" windowHeight="11511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4 к. ФЭВТ" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t xml:space="preserve">    УТВЕРЖДАЮ:</t>
   </si>
@@ -85,9 +85,6 @@
     <t>5- 6</t>
   </si>
   <si>
-    <t>ТЕРМОДИН., СТАТИСТ.</t>
-  </si>
-  <si>
     <t>проф. Крючков С.В.</t>
   </si>
   <si>
@@ -100,19 +97,10 @@
     <t xml:space="preserve"> 9-10</t>
   </si>
   <si>
-    <t>ДЕЛ.ОБЩЕН.В ПРОФ.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 11-12</t>
   </si>
   <si>
     <t>ВТОРНИК</t>
-  </si>
-  <si>
-    <t>В 803</t>
-  </si>
-  <si>
-    <t>Васильева В.Д.</t>
   </si>
   <si>
     <t>СРЕДА</t>
@@ -125,12 +113,6 @@
   </si>
   <si>
     <t>СУББОТА</t>
-  </si>
-  <si>
-    <t>ВКР</t>
-  </si>
-  <si>
-    <t>Гилка В.В.</t>
   </si>
   <si>
     <t>В 902в</t>
@@ -146,6 +128,48 @@
   </si>
   <si>
     <t>Начальник учебного отдела_________________ Фролов Е.М.</t>
+  </si>
+  <si>
+    <t>ГилкаААА В.В.</t>
+  </si>
+  <si>
+    <t>ГилкаБББ В.В.</t>
+  </si>
+  <si>
+    <t>В 803А</t>
+  </si>
+  <si>
+    <t>В 803Б</t>
+  </si>
+  <si>
+    <t>314А</t>
+  </si>
+  <si>
+    <t>314Б</t>
+  </si>
+  <si>
+    <t>ВКР-2</t>
+  </si>
+  <si>
+    <t>ВКР-1</t>
+  </si>
+  <si>
+    <t>ДЕЛ.ОБЩЕН.В ПРОФ.-3</t>
+  </si>
+  <si>
+    <t>ДЕЛ.ОБЩЕН.В ПРОФ.-1</t>
+  </si>
+  <si>
+    <t>ТЕРМОДИН., СТАТИСТ.-4</t>
+  </si>
+  <si>
+    <t>ТЕРМОДИН., СТАТИСТ.-5</t>
+  </si>
+  <si>
+    <t>Васильева В.Д.-1</t>
+  </si>
+  <si>
+    <t>Васильева В.Д.-2</t>
   </si>
 </sst>
 </file>
@@ -4059,17 +4083,153 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4077,423 +4237,287 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="127" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="127" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4800,18 +4824,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:HW262"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="7.84375" customWidth="1"/>
-    <col min="4" max="6" width="7.69140625" customWidth="1"/>
-    <col min="7" max="34" width="9.69140625" customWidth="1"/>
-    <col min="35" max="35" width="11.3046875" customWidth="1"/>
-    <col min="36" max="36" width="7.84375" customWidth="1"/>
-    <col min="37" max="144" width="10.69140625" customWidth="1"/>
+    <col min="1" max="3" width="7.86328125" customWidth="1"/>
+    <col min="4" max="6" width="7.6640625" customWidth="1"/>
+    <col min="7" max="34" width="9.6640625" customWidth="1"/>
+    <col min="35" max="35" width="11.33203125" customWidth="1"/>
+    <col min="36" max="36" width="7.86328125" customWidth="1"/>
+    <col min="37" max="144" width="10.6640625" customWidth="1"/>
     <col min="145" max="256" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:231" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:231" ht="33" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4845,10 +4869,10 @@
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
-      <c r="AF1" s="615"/>
-      <c r="AG1" s="551"/>
-      <c r="AH1" s="551"/>
-      <c r="AI1" s="551"/>
+      <c r="AF1" s="624"/>
+      <c r="AG1" s="543"/>
+      <c r="AH1" s="543"/>
+      <c r="AI1" s="543"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="6"/>
       <c r="AL1" s="6"/>
@@ -5046,7 +5070,7 @@
       <c r="HV1" s="6"/>
       <c r="HW1" s="6"/>
     </row>
-    <row r="2" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5281,7 +5305,7 @@
       <c r="HV2" s="6"/>
       <c r="HW2" s="6"/>
     </row>
-    <row r="3" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5518,7 +5542,7 @@
       <c r="HV3" s="9"/>
       <c r="HW3" s="9"/>
     </row>
-    <row r="4" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -5753,7 +5777,7 @@
       <c r="HV4" s="6"/>
       <c r="HW4" s="6"/>
     </row>
-    <row r="5" spans="1:231" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:231" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -5986,7 +6010,7 @@
       <c r="HV5" s="6"/>
       <c r="HW5" s="6"/>
     </row>
-    <row r="6" spans="1:231" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:231" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A6" s="11" t="s">
         <v>5</v>
       </c>
@@ -6004,48 +6028,48 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="601" t="s">
+      <c r="H6" s="638" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="561"/>
-      <c r="J6" s="561"/>
-      <c r="K6" s="561"/>
-      <c r="L6" s="630" t="s">
+      <c r="I6" s="559"/>
+      <c r="J6" s="559"/>
+      <c r="K6" s="559"/>
+      <c r="L6" s="558" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="561"/>
-      <c r="N6" s="561"/>
-      <c r="O6" s="578"/>
-      <c r="P6" s="577" t="s">
+      <c r="M6" s="559"/>
+      <c r="N6" s="559"/>
+      <c r="O6" s="560"/>
+      <c r="P6" s="600" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="561"/>
-      <c r="R6" s="561"/>
-      <c r="S6" s="578"/>
-      <c r="T6" s="594" t="s">
+      <c r="Q6" s="559"/>
+      <c r="R6" s="559"/>
+      <c r="S6" s="560"/>
+      <c r="T6" s="636" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="561"/>
-      <c r="V6" s="561"/>
-      <c r="W6" s="595"/>
-      <c r="X6" s="560" t="s">
+      <c r="U6" s="559"/>
+      <c r="V6" s="559"/>
+      <c r="W6" s="612"/>
+      <c r="X6" s="626" t="s">
         <v>14</v>
       </c>
-      <c r="Y6" s="561"/>
-      <c r="Z6" s="561"/>
-      <c r="AA6" s="561"/>
-      <c r="AB6" s="630" t="s">
+      <c r="Y6" s="559"/>
+      <c r="Z6" s="559"/>
+      <c r="AA6" s="559"/>
+      <c r="AB6" s="558" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="561"/>
-      <c r="AD6" s="561"/>
-      <c r="AE6" s="578"/>
-      <c r="AF6" s="622" t="s">
+      <c r="AC6" s="559"/>
+      <c r="AD6" s="559"/>
+      <c r="AE6" s="560"/>
+      <c r="AF6" s="620" t="s">
         <v>16</v>
       </c>
-      <c r="AG6" s="561"/>
-      <c r="AH6" s="561"/>
-      <c r="AI6" s="614"/>
+      <c r="AG6" s="559"/>
+      <c r="AH6" s="559"/>
+      <c r="AI6" s="621"/>
       <c r="AJ6" s="14"/>
       <c r="AK6" s="6"/>
       <c r="AL6" s="6"/>
@@ -6243,7 +6267,7 @@
       <c r="HV6" s="6"/>
       <c r="HW6" s="6"/>
     </row>
-    <row r="7" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A7" s="278"/>
       <c r="B7" s="278"/>
       <c r="C7" s="278"/>
@@ -6476,16 +6500,16 @@
       <c r="HV7" s="6"/>
       <c r="HW7" s="6"/>
     </row>
-    <row r="8" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="554"/>
-      <c r="B8" s="554"/>
-      <c r="C8" s="554"/>
-      <c r="D8" s="554"/>
-      <c r="E8" s="554"/>
-      <c r="F8" s="608" t="s">
+    <row r="8" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="557"/>
+      <c r="B8" s="557"/>
+      <c r="C8" s="557"/>
+      <c r="D8" s="557"/>
+      <c r="E8" s="557"/>
+      <c r="F8" s="630" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="645" t="s">
+      <c r="G8" s="569" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="281"/>
@@ -6713,14 +6737,14 @@
       <c r="HV8" s="6"/>
       <c r="HW8" s="6"/>
     </row>
-    <row r="9" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="535"/>
-      <c r="B9" s="535"/>
-      <c r="C9" s="535"/>
-      <c r="D9" s="535"/>
-      <c r="E9" s="535"/>
-      <c r="F9" s="609"/>
-      <c r="G9" s="543"/>
+    <row r="9" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="538"/>
+      <c r="B9" s="538"/>
+      <c r="C9" s="538"/>
+      <c r="D9" s="538"/>
+      <c r="E9" s="538"/>
+      <c r="F9" s="631"/>
+      <c r="G9" s="552"/>
       <c r="H9" s="265"/>
       <c r="I9" s="54"/>
       <c r="J9" s="54"/>
@@ -6946,14 +6970,14 @@
       <c r="HV9" s="6"/>
       <c r="HW9" s="6"/>
     </row>
-    <row r="10" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="536"/>
-      <c r="B10" s="536"/>
-      <c r="C10" s="536"/>
-      <c r="D10" s="536"/>
-      <c r="E10" s="536"/>
-      <c r="F10" s="609"/>
-      <c r="G10" s="544"/>
+    <row r="10" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="539"/>
+      <c r="B10" s="539"/>
+      <c r="C10" s="539"/>
+      <c r="D10" s="539"/>
+      <c r="E10" s="539"/>
+      <c r="F10" s="631"/>
+      <c r="G10" s="566"/>
       <c r="H10" s="287"/>
       <c r="I10" s="93"/>
       <c r="J10" s="93"/>
@@ -7180,21 +7204,21 @@
       <c r="HW10" s="6"/>
     </row>
     <row r="11" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="556">
+      <c r="A11" s="583">
         <v>7</v>
       </c>
-      <c r="B11" s="534">
+      <c r="B11" s="563">
         <v>6</v>
       </c>
-      <c r="C11" s="534">
+      <c r="C11" s="563">
         <v>3</v>
       </c>
-      <c r="D11" s="534">
+      <c r="D11" s="563">
         <v>1</v>
       </c>
-      <c r="E11" s="552"/>
-      <c r="F11" s="609"/>
-      <c r="G11" s="572" t="s">
+      <c r="E11" s="537"/>
+      <c r="F11" s="631"/>
+      <c r="G11" s="565" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="265"/>
@@ -7422,14 +7446,14 @@
       <c r="HV11" s="6"/>
       <c r="HW11" s="6"/>
     </row>
-    <row r="12" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="535"/>
-      <c r="B12" s="535"/>
-      <c r="C12" s="535"/>
-      <c r="D12" s="535"/>
-      <c r="E12" s="535"/>
-      <c r="F12" s="609"/>
-      <c r="G12" s="543"/>
+    <row r="12" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="538"/>
+      <c r="B12" s="538"/>
+      <c r="C12" s="538"/>
+      <c r="D12" s="538"/>
+      <c r="E12" s="538"/>
+      <c r="F12" s="631"/>
+      <c r="G12" s="552"/>
       <c r="H12" s="265"/>
       <c r="I12" s="54"/>
       <c r="J12" s="54"/>
@@ -7655,14 +7679,14 @@
       <c r="HV12" s="6"/>
       <c r="HW12" s="6"/>
     </row>
-    <row r="13" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="536"/>
-      <c r="B13" s="536"/>
-      <c r="C13" s="536"/>
-      <c r="D13" s="536"/>
-      <c r="E13" s="536"/>
-      <c r="F13" s="609"/>
-      <c r="G13" s="544"/>
+    <row r="13" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="539"/>
+      <c r="B13" s="539"/>
+      <c r="C13" s="539"/>
+      <c r="D13" s="539"/>
+      <c r="E13" s="539"/>
+      <c r="F13" s="631"/>
+      <c r="G13" s="566"/>
       <c r="H13" s="262"/>
       <c r="I13" s="70"/>
       <c r="J13" s="70"/>
@@ -7888,54 +7912,54 @@
       <c r="HV13" s="6"/>
       <c r="HW13" s="6"/>
     </row>
-    <row r="14" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="534">
+    <row r="14" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="563">
         <v>20</v>
       </c>
-      <c r="B14" s="534">
+      <c r="B14" s="563">
         <v>20</v>
       </c>
-      <c r="C14" s="534">
+      <c r="C14" s="563">
         <v>17</v>
       </c>
-      <c r="D14" s="534">
+      <c r="D14" s="563">
         <v>15</v>
       </c>
-      <c r="E14" s="552"/>
-      <c r="F14" s="609"/>
-      <c r="G14" s="587" t="s">
+      <c r="E14" s="537"/>
+      <c r="F14" s="631"/>
+      <c r="G14" s="601" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="258"/>
       <c r="I14" s="58"/>
       <c r="J14" s="58"/>
       <c r="K14" s="259"/>
-      <c r="L14" s="557"/>
-      <c r="M14" s="547"/>
+      <c r="L14" s="584"/>
+      <c r="M14" s="580"/>
       <c r="N14" s="185"/>
       <c r="O14" s="165"/>
-      <c r="P14" s="545"/>
-      <c r="Q14" s="547"/>
+      <c r="P14" s="579"/>
+      <c r="Q14" s="580"/>
       <c r="R14" s="303"/>
       <c r="S14" s="304"/>
-      <c r="T14" s="585" t="s">
-        <v>26</v>
+      <c r="T14" s="644" t="s">
+        <v>45</v>
       </c>
-      <c r="U14" s="586"/>
-      <c r="V14" s="586"/>
-      <c r="W14" s="586"/>
-      <c r="X14" s="646" t="s">
-        <v>35</v>
+      <c r="U14" s="571"/>
+      <c r="V14" s="571"/>
+      <c r="W14" s="571"/>
+      <c r="X14" s="570" t="s">
+        <v>42</v>
       </c>
-      <c r="Y14" s="586"/>
-      <c r="Z14" s="586"/>
-      <c r="AA14" s="617"/>
-      <c r="AB14" s="557" t="s">
-        <v>21</v>
+      <c r="Y14" s="571"/>
+      <c r="Z14" s="571"/>
+      <c r="AA14" s="572"/>
+      <c r="AB14" s="584" t="s">
+        <v>46</v>
       </c>
-      <c r="AC14" s="546"/>
-      <c r="AD14" s="546"/>
-      <c r="AE14" s="547"/>
+      <c r="AC14" s="549"/>
+      <c r="AD14" s="549"/>
+      <c r="AE14" s="580"/>
       <c r="AF14" s="26"/>
       <c r="AG14" s="26"/>
       <c r="AH14" s="26"/>
@@ -8137,24 +8161,24 @@
       <c r="HV14" s="6"/>
       <c r="HW14" s="6"/>
     </row>
-    <row r="15" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="535"/>
-      <c r="B15" s="535"/>
-      <c r="C15" s="535"/>
-      <c r="D15" s="535"/>
-      <c r="E15" s="535"/>
-      <c r="F15" s="609"/>
-      <c r="G15" s="543"/>
+    <row r="15" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A15" s="538"/>
+      <c r="B15" s="538"/>
+      <c r="C15" s="538"/>
+      <c r="D15" s="538"/>
+      <c r="E15" s="538"/>
+      <c r="F15" s="631"/>
+      <c r="G15" s="552"/>
       <c r="H15" s="305"/>
       <c r="I15" s="84"/>
       <c r="J15" s="84"/>
       <c r="K15" s="261"/>
-      <c r="L15" s="582"/>
-      <c r="M15" s="539"/>
+      <c r="L15" s="573"/>
+      <c r="M15" s="541"/>
       <c r="N15" s="65"/>
       <c r="O15" s="245"/>
-      <c r="P15" s="562"/>
-      <c r="Q15" s="539"/>
+      <c r="P15" s="556"/>
+      <c r="Q15" s="541"/>
       <c r="R15" s="166"/>
       <c r="S15" s="62"/>
       <c r="T15" s="214"/>
@@ -8370,49 +8394,49 @@
       <c r="HV15" s="6"/>
       <c r="HW15" s="6"/>
     </row>
-    <row r="16" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A16" s="536"/>
-      <c r="B16" s="536"/>
-      <c r="C16" s="536"/>
-      <c r="D16" s="536"/>
-      <c r="E16" s="536"/>
-      <c r="F16" s="609"/>
-      <c r="G16" s="588"/>
+    <row r="16" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A16" s="539"/>
+      <c r="B16" s="539"/>
+      <c r="C16" s="539"/>
+      <c r="D16" s="539"/>
+      <c r="E16" s="539"/>
+      <c r="F16" s="631"/>
+      <c r="G16" s="602"/>
       <c r="H16" s="306"/>
       <c r="I16" s="307"/>
       <c r="J16" s="307"/>
       <c r="K16" s="308"/>
-      <c r="L16" s="590"/>
-      <c r="M16" s="539"/>
+      <c r="L16" s="581"/>
+      <c r="M16" s="541"/>
       <c r="N16" s="309"/>
       <c r="O16" s="310"/>
-      <c r="P16" s="540"/>
-      <c r="Q16" s="539"/>
+      <c r="P16" s="577"/>
+      <c r="Q16" s="541"/>
       <c r="R16" s="311"/>
       <c r="S16" s="216"/>
       <c r="T16" s="312" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="U16" s="313"/>
       <c r="V16" s="313"/>
       <c r="W16" s="314" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="X16" s="312" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y16" s="313"/>
       <c r="Z16" s="315"/>
       <c r="AA16" s="316" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AB16" s="312" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC16" s="313"/>
       <c r="AD16" s="313"/>
-      <c r="AE16" s="316">
-        <v>314</v>
+      <c r="AE16" s="316" t="s">
+        <v>40</v>
       </c>
       <c r="AF16" s="26"/>
       <c r="AG16" s="26"/>
@@ -8615,56 +8639,56 @@
       <c r="HV16" s="6"/>
       <c r="HW16" s="6"/>
     </row>
-    <row r="17" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="552">
+    <row r="17" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="537">
         <v>0</v>
       </c>
-      <c r="B17" s="552">
+      <c r="B17" s="537">
         <v>0</v>
       </c>
-      <c r="C17" s="552">
+      <c r="C17" s="537">
         <v>0</v>
       </c>
-      <c r="D17" s="534">
+      <c r="D17" s="563">
         <v>29</v>
       </c>
-      <c r="E17" s="552">
+      <c r="E17" s="537">
         <v>0</v>
       </c>
-      <c r="F17" s="609"/>
-      <c r="G17" s="589" t="s">
-        <v>23</v>
+      <c r="F17" s="631"/>
+      <c r="G17" s="587" t="s">
+        <v>22</v>
       </c>
       <c r="H17" s="318"/>
       <c r="I17" s="319"/>
       <c r="J17" s="319"/>
       <c r="K17" s="320"/>
-      <c r="L17" s="541"/>
-      <c r="M17" s="539"/>
+      <c r="L17" s="599"/>
+      <c r="M17" s="541"/>
       <c r="N17" s="82"/>
       <c r="O17" s="321"/>
-      <c r="P17" s="538"/>
-      <c r="Q17" s="539"/>
+      <c r="P17" s="576"/>
+      <c r="Q17" s="541"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
-      <c r="T17" s="624" t="s">
-        <v>35</v>
+      <c r="T17" s="613" t="s">
+        <v>43</v>
       </c>
-      <c r="U17" s="551"/>
-      <c r="V17" s="551"/>
-      <c r="W17" s="551"/>
-      <c r="X17" s="592" t="s">
-        <v>26</v>
+      <c r="U17" s="543"/>
+      <c r="V17" s="543"/>
+      <c r="W17" s="543"/>
+      <c r="X17" s="555" t="s">
+        <v>44</v>
       </c>
-      <c r="Y17" s="551"/>
-      <c r="Z17" s="551"/>
-      <c r="AA17" s="539"/>
-      <c r="AB17" s="618" t="s">
-        <v>21</v>
+      <c r="Y17" s="543"/>
+      <c r="Z17" s="543"/>
+      <c r="AA17" s="541"/>
+      <c r="AB17" s="588" t="s">
+        <v>47</v>
       </c>
-      <c r="AC17" s="619"/>
-      <c r="AD17" s="619"/>
-      <c r="AE17" s="620"/>
+      <c r="AC17" s="589"/>
+      <c r="AD17" s="589"/>
+      <c r="AE17" s="590"/>
       <c r="AF17" s="322"/>
       <c r="AG17" s="322"/>
       <c r="AH17" s="322"/>
@@ -8866,14 +8890,14 @@
       <c r="HV17" s="6"/>
       <c r="HW17" s="6"/>
     </row>
-    <row r="18" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="535"/>
-      <c r="B18" s="535"/>
-      <c r="C18" s="535"/>
-      <c r="D18" s="535"/>
-      <c r="E18" s="535"/>
-      <c r="F18" s="609"/>
-      <c r="G18" s="543"/>
+    <row r="18" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="538"/>
+      <c r="B18" s="538"/>
+      <c r="C18" s="538"/>
+      <c r="D18" s="538"/>
+      <c r="E18" s="538"/>
+      <c r="F18" s="631"/>
+      <c r="G18" s="552"/>
       <c r="H18" s="260"/>
       <c r="I18" s="67"/>
       <c r="J18" s="67"/>
@@ -9099,24 +9123,24 @@
       <c r="HV18" s="6"/>
       <c r="HW18" s="6"/>
     </row>
-    <row r="19" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A19" s="536"/>
-      <c r="B19" s="536"/>
-      <c r="C19" s="536"/>
-      <c r="D19" s="536"/>
-      <c r="E19" s="536"/>
-      <c r="F19" s="609"/>
-      <c r="G19" s="544"/>
+    <row r="19" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A19" s="539"/>
+      <c r="B19" s="539"/>
+      <c r="C19" s="539"/>
+      <c r="D19" s="539"/>
+      <c r="E19" s="539"/>
+      <c r="F19" s="631"/>
+      <c r="G19" s="566"/>
       <c r="H19" s="324"/>
       <c r="I19" s="325"/>
       <c r="J19" s="89"/>
       <c r="K19" s="268"/>
-      <c r="L19" s="643"/>
-      <c r="M19" s="566"/>
+      <c r="L19" s="582"/>
+      <c r="M19" s="568"/>
       <c r="N19" s="116"/>
       <c r="O19" s="252"/>
-      <c r="P19" s="611"/>
-      <c r="Q19" s="566"/>
+      <c r="P19" s="639"/>
+      <c r="Q19" s="568"/>
       <c r="R19" s="197"/>
       <c r="S19" s="326"/>
       <c r="T19" s="222" t="s">
@@ -9125,23 +9149,23 @@
       <c r="U19" s="101"/>
       <c r="V19" s="327"/>
       <c r="W19" s="103" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="X19" s="222" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="Y19" s="101"/>
       <c r="Z19" s="101"/>
       <c r="AA19" s="223" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AB19" s="222" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC19" s="101"/>
       <c r="AD19" s="101"/>
-      <c r="AE19" s="223">
-        <v>314</v>
+      <c r="AE19" s="223" t="s">
+        <v>41</v>
       </c>
       <c r="AF19" s="26"/>
       <c r="AG19" s="26"/>
@@ -9344,15 +9368,15 @@
       <c r="HV19" s="6"/>
       <c r="HW19" s="6"/>
     </row>
-    <row r="20" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="537"/>
-      <c r="B20" s="537"/>
-      <c r="C20" s="537"/>
-      <c r="D20" s="537"/>
-      <c r="E20" s="537"/>
-      <c r="F20" s="609"/>
-      <c r="G20" s="589" t="s">
-        <v>25</v>
+    <row r="20" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="544"/>
+      <c r="B20" s="544"/>
+      <c r="C20" s="544"/>
+      <c r="D20" s="544"/>
+      <c r="E20" s="544"/>
+      <c r="F20" s="631"/>
+      <c r="G20" s="587" t="s">
+        <v>24</v>
       </c>
       <c r="H20" s="169"/>
       <c r="I20" s="26"/>
@@ -9360,12 +9384,12 @@
       <c r="K20" s="168"/>
       <c r="L20" s="225"/>
       <c r="M20" s="146"/>
-      <c r="N20" s="628"/>
-      <c r="O20" s="539"/>
+      <c r="N20" s="585"/>
+      <c r="O20" s="541"/>
       <c r="P20" s="158"/>
       <c r="Q20" s="159"/>
-      <c r="R20" s="616"/>
-      <c r="S20" s="551"/>
+      <c r="R20" s="625"/>
+      <c r="S20" s="543"/>
       <c r="T20" s="154"/>
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
@@ -9579,26 +9603,26 @@
       <c r="HV20" s="6"/>
       <c r="HW20" s="6"/>
     </row>
-    <row r="21" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="535"/>
-      <c r="B21" s="535"/>
-      <c r="C21" s="535"/>
-      <c r="D21" s="535"/>
-      <c r="E21" s="535"/>
-      <c r="F21" s="609"/>
-      <c r="G21" s="543"/>
+    <row r="21" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A21" s="538"/>
+      <c r="B21" s="538"/>
+      <c r="C21" s="538"/>
+      <c r="D21" s="538"/>
+      <c r="E21" s="538"/>
+      <c r="F21" s="631"/>
+      <c r="G21" s="552"/>
       <c r="H21" s="169"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
       <c r="K21" s="168"/>
       <c r="L21" s="225"/>
       <c r="M21" s="146"/>
-      <c r="N21" s="593"/>
-      <c r="O21" s="539"/>
+      <c r="N21" s="545"/>
+      <c r="O21" s="541"/>
       <c r="P21" s="158"/>
       <c r="Q21" s="159"/>
-      <c r="R21" s="625"/>
-      <c r="S21" s="551"/>
+      <c r="R21" s="609"/>
+      <c r="S21" s="543"/>
       <c r="T21" s="154"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
@@ -9812,26 +9836,26 @@
       <c r="HV21" s="6"/>
       <c r="HW21" s="6"/>
     </row>
-    <row r="22" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="536"/>
-      <c r="B22" s="536"/>
-      <c r="C22" s="536"/>
-      <c r="D22" s="536"/>
-      <c r="E22" s="536"/>
-      <c r="F22" s="609"/>
-      <c r="G22" s="544"/>
+    <row r="22" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="539"/>
+      <c r="B22" s="539"/>
+      <c r="C22" s="539"/>
+      <c r="D22" s="539"/>
+      <c r="E22" s="539"/>
+      <c r="F22" s="631"/>
+      <c r="G22" s="566"/>
       <c r="H22" s="332"/>
       <c r="I22" s="89"/>
       <c r="J22" s="89"/>
       <c r="K22" s="194"/>
       <c r="L22" s="333"/>
       <c r="M22" s="334"/>
-      <c r="N22" s="540"/>
-      <c r="O22" s="539"/>
+      <c r="N22" s="577"/>
+      <c r="O22" s="541"/>
       <c r="P22" s="335"/>
       <c r="Q22" s="336"/>
-      <c r="R22" s="600"/>
-      <c r="S22" s="551"/>
+      <c r="R22" s="542"/>
+      <c r="S22" s="543"/>
       <c r="T22" s="230"/>
       <c r="U22" s="91"/>
       <c r="V22" s="91"/>
@@ -10045,15 +10069,15 @@
       <c r="HV22" s="6"/>
       <c r="HW22" s="6"/>
     </row>
-    <row r="23" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="537"/>
-      <c r="B23" s="537"/>
-      <c r="C23" s="537"/>
-      <c r="D23" s="537"/>
-      <c r="E23" s="537"/>
-      <c r="F23" s="609"/>
-      <c r="G23" s="563" t="s">
-        <v>27</v>
+    <row r="23" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="544"/>
+      <c r="B23" s="544"/>
+      <c r="C23" s="544"/>
+      <c r="D23" s="544"/>
+      <c r="E23" s="544"/>
+      <c r="F23" s="631"/>
+      <c r="G23" s="578" t="s">
+        <v>25</v>
       </c>
       <c r="H23" s="169"/>
       <c r="I23" s="26"/>
@@ -10061,12 +10085,12 @@
       <c r="K23" s="168"/>
       <c r="L23" s="225"/>
       <c r="M23" s="146"/>
-      <c r="N23" s="538"/>
-      <c r="O23" s="539"/>
+      <c r="N23" s="576"/>
+      <c r="O23" s="541"/>
       <c r="P23" s="293"/>
       <c r="Q23" s="340"/>
-      <c r="R23" s="627"/>
-      <c r="S23" s="551"/>
+      <c r="R23" s="610"/>
+      <c r="S23" s="543"/>
       <c r="T23" s="289"/>
       <c r="U23" s="34"/>
       <c r="V23" s="34"/>
@@ -10280,14 +10304,14 @@
       <c r="HV23" s="6"/>
       <c r="HW23" s="6"/>
     </row>
-    <row r="24" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="535"/>
-      <c r="B24" s="535"/>
-      <c r="C24" s="535"/>
-      <c r="D24" s="535"/>
-      <c r="E24" s="535"/>
-      <c r="F24" s="609"/>
-      <c r="G24" s="543"/>
+    <row r="24" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="538"/>
+      <c r="B24" s="538"/>
+      <c r="C24" s="538"/>
+      <c r="D24" s="538"/>
+      <c r="E24" s="538"/>
+      <c r="F24" s="631"/>
+      <c r="G24" s="552"/>
       <c r="H24" s="169"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
@@ -10513,26 +10537,26 @@
       <c r="HV24" s="6"/>
       <c r="HW24" s="6"/>
     </row>
-    <row r="25" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="536"/>
-      <c r="B25" s="536"/>
-      <c r="C25" s="536"/>
-      <c r="D25" s="536"/>
-      <c r="E25" s="536"/>
-      <c r="F25" s="610"/>
-      <c r="G25" s="564"/>
+    <row r="25" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="539"/>
+      <c r="B25" s="539"/>
+      <c r="C25" s="539"/>
+      <c r="D25" s="539"/>
+      <c r="E25" s="539"/>
+      <c r="F25" s="632"/>
+      <c r="G25" s="562"/>
       <c r="H25" s="169"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
       <c r="K25" s="168"/>
       <c r="L25" s="341"/>
       <c r="M25" s="342"/>
-      <c r="N25" s="549"/>
-      <c r="O25" s="539"/>
+      <c r="N25" s="593"/>
+      <c r="O25" s="541"/>
       <c r="P25" s="343"/>
       <c r="Q25" s="344"/>
-      <c r="R25" s="550"/>
-      <c r="S25" s="551"/>
+      <c r="R25" s="650"/>
+      <c r="S25" s="543"/>
       <c r="T25" s="289"/>
       <c r="U25" s="34"/>
       <c r="V25" s="34"/>
@@ -10746,16 +10770,16 @@
       <c r="HV25" s="6"/>
       <c r="HW25" s="6"/>
     </row>
-    <row r="26" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="537"/>
-      <c r="B26" s="554"/>
-      <c r="C26" s="554"/>
-      <c r="D26" s="554"/>
-      <c r="E26" s="554"/>
-      <c r="F26" s="579" t="s">
-        <v>28</v>
+    <row r="26" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="544"/>
+      <c r="B26" s="557"/>
+      <c r="C26" s="557"/>
+      <c r="D26" s="557"/>
+      <c r="E26" s="557"/>
+      <c r="F26" s="640" t="s">
+        <v>26</v>
       </c>
-      <c r="G26" s="567" t="s">
+      <c r="G26" s="646" t="s">
         <v>18</v>
       </c>
       <c r="H26" s="348"/>
@@ -10983,14 +11007,14 @@
       <c r="HV26" s="6"/>
       <c r="HW26" s="6"/>
     </row>
-    <row r="27" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="535"/>
-      <c r="B27" s="535"/>
-      <c r="C27" s="535"/>
-      <c r="D27" s="535"/>
-      <c r="E27" s="535"/>
-      <c r="F27" s="580"/>
-      <c r="G27" s="543"/>
+    <row r="27" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="538"/>
+      <c r="B27" s="538"/>
+      <c r="C27" s="538"/>
+      <c r="D27" s="538"/>
+      <c r="E27" s="538"/>
+      <c r="F27" s="604"/>
+      <c r="G27" s="552"/>
       <c r="H27" s="154"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
@@ -11216,14 +11240,14 @@
       <c r="HV27" s="6"/>
       <c r="HW27" s="6"/>
     </row>
-    <row r="28" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="536"/>
-      <c r="B28" s="536"/>
-      <c r="C28" s="536"/>
-      <c r="D28" s="536"/>
-      <c r="E28" s="536"/>
-      <c r="F28" s="580"/>
-      <c r="G28" s="544"/>
+    <row r="28" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="539"/>
+      <c r="B28" s="539"/>
+      <c r="C28" s="539"/>
+      <c r="D28" s="539"/>
+      <c r="E28" s="539"/>
+      <c r="F28" s="604"/>
+      <c r="G28" s="566"/>
       <c r="H28" s="154"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
@@ -11449,22 +11473,22 @@
       <c r="HV28" s="6"/>
       <c r="HW28" s="6"/>
     </row>
-    <row r="29" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="553">
+    <row r="29" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="633">
         <v>8</v>
       </c>
-      <c r="B29" s="534">
+      <c r="B29" s="563">
         <v>7</v>
       </c>
-      <c r="C29" s="534">
+      <c r="C29" s="563">
         <v>4</v>
       </c>
-      <c r="D29" s="534">
+      <c r="D29" s="563">
         <v>2</v>
       </c>
-      <c r="E29" s="552"/>
-      <c r="F29" s="580"/>
-      <c r="G29" s="572" t="s">
+      <c r="E29" s="537"/>
+      <c r="F29" s="604"/>
+      <c r="G29" s="565" t="s">
         <v>19</v>
       </c>
       <c r="H29" s="356"/>
@@ -11692,14 +11716,14 @@
       <c r="HV29" s="6"/>
       <c r="HW29" s="6"/>
     </row>
-    <row r="30" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="535"/>
-      <c r="B30" s="535"/>
-      <c r="C30" s="535"/>
-      <c r="D30" s="535"/>
-      <c r="E30" s="535"/>
-      <c r="F30" s="580"/>
-      <c r="G30" s="543"/>
+    <row r="30" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="538"/>
+      <c r="B30" s="538"/>
+      <c r="C30" s="538"/>
+      <c r="D30" s="538"/>
+      <c r="E30" s="538"/>
+      <c r="F30" s="604"/>
+      <c r="G30" s="552"/>
       <c r="H30" s="154"/>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
@@ -11925,14 +11949,14 @@
       <c r="HV30" s="6"/>
       <c r="HW30" s="6"/>
     </row>
-    <row r="31" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A31" s="536"/>
-      <c r="B31" s="536"/>
-      <c r="C31" s="536"/>
-      <c r="D31" s="536"/>
-      <c r="E31" s="536"/>
-      <c r="F31" s="580"/>
-      <c r="G31" s="544"/>
+    <row r="31" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A31" s="539"/>
+      <c r="B31" s="539"/>
+      <c r="C31" s="539"/>
+      <c r="D31" s="539"/>
+      <c r="E31" s="539"/>
+      <c r="F31" s="604"/>
+      <c r="G31" s="566"/>
       <c r="H31" s="333"/>
       <c r="I31" s="197"/>
       <c r="J31" s="197"/>
@@ -12158,26 +12182,26 @@
       <c r="HV31" s="6"/>
       <c r="HW31" s="6"/>
     </row>
-    <row r="32" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="534">
+    <row r="32" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="563">
         <v>21</v>
       </c>
-      <c r="B32" s="534">
+      <c r="B32" s="563">
         <v>21</v>
       </c>
-      <c r="C32" s="534">
+      <c r="C32" s="563">
         <v>18</v>
       </c>
-      <c r="D32" s="534">
+      <c r="D32" s="563">
         <v>16</v>
       </c>
-      <c r="E32" s="552"/>
-      <c r="F32" s="580"/>
-      <c r="G32" s="650" t="s">
+      <c r="E32" s="537"/>
+      <c r="F32" s="604"/>
+      <c r="G32" s="551" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="592"/>
-      <c r="I32" s="539"/>
+      <c r="H32" s="555"/>
+      <c r="I32" s="541"/>
       <c r="J32" s="142"/>
       <c r="K32" s="143"/>
       <c r="L32" s="106"/>
@@ -12188,10 +12212,10 @@
       <c r="Q32" s="58"/>
       <c r="R32" s="58"/>
       <c r="S32" s="59"/>
-      <c r="T32" s="591"/>
-      <c r="U32" s="546"/>
-      <c r="V32" s="546"/>
-      <c r="W32" s="546"/>
+      <c r="T32" s="564"/>
+      <c r="U32" s="549"/>
+      <c r="V32" s="549"/>
+      <c r="W32" s="549"/>
       <c r="X32" s="360"/>
       <c r="Y32" s="361"/>
       <c r="Z32" s="361"/>
@@ -12200,10 +12224,10 @@
       <c r="AC32" s="364"/>
       <c r="AD32" s="364"/>
       <c r="AE32" s="365"/>
-      <c r="AF32" s="545"/>
-      <c r="AG32" s="546"/>
-      <c r="AH32" s="546"/>
-      <c r="AI32" s="547"/>
+      <c r="AF32" s="579"/>
+      <c r="AG32" s="549"/>
+      <c r="AH32" s="549"/>
+      <c r="AI32" s="580"/>
       <c r="AJ32" s="144"/>
       <c r="AK32" s="6"/>
       <c r="AL32" s="6"/>
@@ -12401,16 +12425,16 @@
       <c r="HV32" s="6"/>
       <c r="HW32" s="6"/>
     </row>
-    <row r="33" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="535"/>
-      <c r="B33" s="535"/>
-      <c r="C33" s="535"/>
-      <c r="D33" s="535"/>
-      <c r="E33" s="535"/>
-      <c r="F33" s="580"/>
-      <c r="G33" s="543"/>
-      <c r="H33" s="582"/>
-      <c r="I33" s="539"/>
+    <row r="33" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A33" s="538"/>
+      <c r="B33" s="538"/>
+      <c r="C33" s="538"/>
+      <c r="D33" s="538"/>
+      <c r="E33" s="538"/>
+      <c r="F33" s="604"/>
+      <c r="G33" s="552"/>
+      <c r="H33" s="573"/>
+      <c r="I33" s="541"/>
       <c r="J33" s="6"/>
       <c r="K33" s="146"/>
       <c r="L33" s="26"/>
@@ -12421,10 +12445,10 @@
       <c r="Q33" s="61"/>
       <c r="R33" s="61"/>
       <c r="S33" s="99"/>
-      <c r="T33" s="603"/>
-      <c r="U33" s="551"/>
-      <c r="V33" s="551"/>
-      <c r="W33" s="551"/>
+      <c r="T33" s="627"/>
+      <c r="U33" s="543"/>
+      <c r="V33" s="543"/>
+      <c r="W33" s="543"/>
       <c r="X33" s="366"/>
       <c r="Y33" s="188"/>
       <c r="Z33" s="317"/>
@@ -12634,16 +12658,16 @@
       <c r="HV33" s="6"/>
       <c r="HW33" s="6"/>
     </row>
-    <row r="34" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="536"/>
-      <c r="B34" s="536"/>
-      <c r="C34" s="536"/>
-      <c r="D34" s="536"/>
-      <c r="E34" s="536"/>
-      <c r="F34" s="580"/>
-      <c r="G34" s="632"/>
-      <c r="H34" s="590"/>
-      <c r="I34" s="539"/>
+    <row r="34" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="539"/>
+      <c r="B34" s="539"/>
+      <c r="C34" s="539"/>
+      <c r="D34" s="539"/>
+      <c r="E34" s="539"/>
+      <c r="F34" s="604"/>
+      <c r="G34" s="553"/>
+      <c r="H34" s="581"/>
+      <c r="I34" s="541"/>
       <c r="J34" s="149"/>
       <c r="K34" s="367"/>
       <c r="L34" s="150"/>
@@ -12655,8 +12679,8 @@
       <c r="R34" s="73"/>
       <c r="S34" s="100"/>
       <c r="T34" s="229"/>
-      <c r="U34" s="600"/>
-      <c r="V34" s="551"/>
+      <c r="U34" s="542"/>
+      <c r="V34" s="543"/>
       <c r="W34" s="228"/>
       <c r="X34" s="368"/>
       <c r="Y34" s="317"/>
@@ -12867,26 +12891,26 @@
       <c r="HV34" s="6"/>
       <c r="HW34" s="6"/>
     </row>
-    <row r="35" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="552">
+    <row r="35" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="537">
         <v>0</v>
       </c>
-      <c r="B35" s="552">
+      <c r="B35" s="537">
         <v>0</v>
       </c>
-      <c r="C35" s="552">
+      <c r="C35" s="537">
         <v>0</v>
       </c>
-      <c r="D35" s="534">
+      <c r="D35" s="563">
         <v>30</v>
       </c>
-      <c r="E35" s="552"/>
-      <c r="F35" s="580"/>
-      <c r="G35" s="589" t="s">
-        <v>23</v>
+      <c r="E35" s="537"/>
+      <c r="F35" s="604"/>
+      <c r="G35" s="587" t="s">
+        <v>22</v>
       </c>
-      <c r="H35" s="541"/>
-      <c r="I35" s="539"/>
+      <c r="H35" s="599"/>
+      <c r="I35" s="541"/>
       <c r="J35" s="6"/>
       <c r="K35" s="146"/>
       <c r="L35" s="54"/>
@@ -12909,10 +12933,10 @@
       <c r="AC35" s="10"/>
       <c r="AD35" s="10"/>
       <c r="AE35" s="10"/>
-      <c r="AF35" s="570"/>
-      <c r="AG35" s="551"/>
-      <c r="AH35" s="551"/>
-      <c r="AI35" s="539"/>
+      <c r="AF35" s="592"/>
+      <c r="AG35" s="543"/>
+      <c r="AH35" s="543"/>
+      <c r="AI35" s="541"/>
       <c r="AJ35" s="152"/>
       <c r="AK35" s="6"/>
       <c r="AL35" s="6"/>
@@ -13110,14 +13134,14 @@
       <c r="HV35" s="6"/>
       <c r="HW35" s="6"/>
     </row>
-    <row r="36" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="535"/>
-      <c r="B36" s="535"/>
-      <c r="C36" s="535"/>
-      <c r="D36" s="535"/>
-      <c r="E36" s="535"/>
-      <c r="F36" s="580"/>
-      <c r="G36" s="543"/>
+    <row r="36" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="538"/>
+      <c r="B36" s="538"/>
+      <c r="C36" s="538"/>
+      <c r="D36" s="538"/>
+      <c r="E36" s="538"/>
+      <c r="F36" s="604"/>
+      <c r="G36" s="552"/>
       <c r="H36" s="225"/>
       <c r="I36" s="85"/>
       <c r="J36" s="6"/>
@@ -13343,16 +13367,16 @@
       <c r="HV36" s="6"/>
       <c r="HW36" s="6"/>
     </row>
-    <row r="37" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A37" s="536"/>
-      <c r="B37" s="536"/>
-      <c r="C37" s="536"/>
-      <c r="D37" s="536"/>
-      <c r="E37" s="536"/>
-      <c r="F37" s="580"/>
-      <c r="G37" s="544"/>
-      <c r="H37" s="649"/>
-      <c r="I37" s="566"/>
+    <row r="37" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A37" s="539"/>
+      <c r="B37" s="539"/>
+      <c r="C37" s="539"/>
+      <c r="D37" s="539"/>
+      <c r="E37" s="539"/>
+      <c r="F37" s="604"/>
+      <c r="G37" s="566"/>
+      <c r="H37" s="567"/>
+      <c r="I37" s="568"/>
       <c r="J37" s="6"/>
       <c r="K37" s="146"/>
       <c r="L37" s="94"/>
@@ -13576,44 +13600,44 @@
       <c r="HV37" s="6"/>
       <c r="HW37" s="6"/>
     </row>
-    <row r="38" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="537"/>
-      <c r="B38" s="537"/>
-      <c r="C38" s="537"/>
-      <c r="D38" s="537"/>
-      <c r="E38" s="537"/>
-      <c r="F38" s="580"/>
-      <c r="G38" s="589" t="s">
-        <v>25</v>
+    <row r="38" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="544"/>
+      <c r="B38" s="544"/>
+      <c r="C38" s="544"/>
+      <c r="D38" s="544"/>
+      <c r="E38" s="544"/>
+      <c r="F38" s="604"/>
+      <c r="G38" s="587" t="s">
+        <v>24</v>
       </c>
       <c r="H38" s="225"/>
       <c r="I38" s="6"/>
-      <c r="J38" s="555"/>
-      <c r="K38" s="547"/>
+      <c r="J38" s="591"/>
+      <c r="K38" s="580"/>
       <c r="L38" s="378"/>
       <c r="M38" s="110"/>
       <c r="N38" s="110"/>
       <c r="O38" s="110"/>
       <c r="P38" s="109"/>
       <c r="Q38" s="110"/>
-      <c r="R38" s="555"/>
-      <c r="S38" s="547"/>
+      <c r="R38" s="591"/>
+      <c r="S38" s="580"/>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
       <c r="W38" s="151"/>
-      <c r="X38" s="570"/>
-      <c r="Y38" s="551"/>
-      <c r="Z38" s="551"/>
-      <c r="AA38" s="539"/>
-      <c r="AB38" s="591"/>
-      <c r="AC38" s="546"/>
-      <c r="AD38" s="546"/>
-      <c r="AE38" s="546"/>
-      <c r="AF38" s="621"/>
-      <c r="AG38" s="586"/>
-      <c r="AH38" s="586"/>
-      <c r="AI38" s="605"/>
+      <c r="X38" s="592"/>
+      <c r="Y38" s="543"/>
+      <c r="Z38" s="543"/>
+      <c r="AA38" s="541"/>
+      <c r="AB38" s="564"/>
+      <c r="AC38" s="549"/>
+      <c r="AD38" s="549"/>
+      <c r="AE38" s="549"/>
+      <c r="AF38" s="618"/>
+      <c r="AG38" s="571"/>
+      <c r="AH38" s="571"/>
+      <c r="AI38" s="619"/>
       <c r="AJ38" s="152"/>
       <c r="AK38" s="6"/>
       <c r="AL38" s="6"/>
@@ -13811,34 +13835,34 @@
       <c r="HV38" s="6"/>
       <c r="HW38" s="6"/>
     </row>
-    <row r="39" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="535"/>
-      <c r="B39" s="535"/>
-      <c r="C39" s="535"/>
-      <c r="D39" s="535"/>
-      <c r="E39" s="535"/>
-      <c r="F39" s="580"/>
-      <c r="G39" s="543"/>
+    <row r="39" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A39" s="538"/>
+      <c r="B39" s="538"/>
+      <c r="C39" s="538"/>
+      <c r="D39" s="538"/>
+      <c r="E39" s="538"/>
+      <c r="F39" s="604"/>
+      <c r="G39" s="552"/>
       <c r="H39" s="225"/>
       <c r="I39" s="6"/>
-      <c r="J39" s="562"/>
-      <c r="K39" s="539"/>
+      <c r="J39" s="556"/>
+      <c r="K39" s="541"/>
       <c r="L39" s="379"/>
       <c r="M39" s="121"/>
       <c r="N39" s="121"/>
       <c r="O39" s="121"/>
       <c r="P39" s="380"/>
       <c r="Q39" s="121"/>
-      <c r="R39" s="562"/>
-      <c r="S39" s="539"/>
+      <c r="R39" s="556"/>
+      <c r="S39" s="541"/>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
       <c r="W39" s="151"/>
-      <c r="X39" s="562"/>
-      <c r="Y39" s="551"/>
-      <c r="Z39" s="551"/>
-      <c r="AA39" s="539"/>
+      <c r="X39" s="556"/>
+      <c r="Y39" s="543"/>
+      <c r="Z39" s="543"/>
+      <c r="AA39" s="541"/>
       <c r="AB39" s="64"/>
       <c r="AC39" s="65"/>
       <c r="AD39" s="65"/>
@@ -14044,33 +14068,33 @@
       <c r="HV39" s="6"/>
       <c r="HW39" s="6"/>
     </row>
-    <row r="40" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="536"/>
-      <c r="B40" s="536"/>
-      <c r="C40" s="536"/>
-      <c r="D40" s="536"/>
-      <c r="E40" s="536"/>
-      <c r="F40" s="580"/>
-      <c r="G40" s="544"/>
+    <row r="40" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="539"/>
+      <c r="B40" s="539"/>
+      <c r="C40" s="539"/>
+      <c r="D40" s="539"/>
+      <c r="E40" s="539"/>
+      <c r="F40" s="604"/>
+      <c r="G40" s="566"/>
       <c r="H40" s="225"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="573"/>
-      <c r="K40" s="539"/>
+      <c r="J40" s="554"/>
+      <c r="K40" s="541"/>
       <c r="L40" s="236"/>
       <c r="M40" s="382"/>
       <c r="N40" s="382"/>
       <c r="O40" s="382"/>
       <c r="P40" s="383"/>
       <c r="Q40" s="382"/>
-      <c r="R40" s="573"/>
-      <c r="S40" s="539"/>
+      <c r="R40" s="554"/>
+      <c r="S40" s="541"/>
       <c r="T40" s="102"/>
       <c r="U40" s="102"/>
       <c r="V40" s="102"/>
       <c r="W40" s="104"/>
       <c r="X40" s="229"/>
-      <c r="Y40" s="600"/>
-      <c r="Z40" s="551"/>
+      <c r="Y40" s="542"/>
+      <c r="Z40" s="543"/>
       <c r="AA40" s="228"/>
       <c r="AB40" s="75"/>
       <c r="AC40" s="76"/>
@@ -14277,28 +14301,28 @@
       <c r="HV40" s="6"/>
       <c r="HW40" s="6"/>
     </row>
-    <row r="41" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="537"/>
-      <c r="B41" s="537"/>
-      <c r="C41" s="537"/>
-      <c r="D41" s="537"/>
-      <c r="E41" s="537"/>
-      <c r="F41" s="580"/>
-      <c r="G41" s="563" t="s">
-        <v>27</v>
+    <row r="41" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="544"/>
+      <c r="B41" s="544"/>
+      <c r="C41" s="544"/>
+      <c r="D41" s="544"/>
+      <c r="E41" s="544"/>
+      <c r="F41" s="604"/>
+      <c r="G41" s="578" t="s">
+        <v>25</v>
       </c>
       <c r="H41" s="384"/>
       <c r="I41" s="142"/>
-      <c r="J41" s="599"/>
-      <c r="K41" s="539"/>
+      <c r="J41" s="605"/>
+      <c r="K41" s="541"/>
       <c r="L41" s="26"/>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
       <c r="O41" s="26"/>
       <c r="P41" s="53"/>
       <c r="Q41" s="54"/>
-      <c r="R41" s="599"/>
-      <c r="S41" s="539"/>
+      <c r="R41" s="605"/>
+      <c r="S41" s="541"/>
       <c r="T41" s="6"/>
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
@@ -14307,10 +14331,10 @@
       <c r="Y41" s="124"/>
       <c r="Z41" s="6"/>
       <c r="AA41" s="151"/>
-      <c r="AB41" s="591"/>
-      <c r="AC41" s="546"/>
-      <c r="AD41" s="546"/>
-      <c r="AE41" s="546"/>
+      <c r="AB41" s="564"/>
+      <c r="AC41" s="549"/>
+      <c r="AD41" s="549"/>
+      <c r="AE41" s="549"/>
       <c r="AF41" s="53"/>
       <c r="AG41" s="54"/>
       <c r="AH41" s="54"/>
@@ -14512,14 +14536,14 @@
       <c r="HV41" s="6"/>
       <c r="HW41" s="6"/>
     </row>
-    <row r="42" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="535"/>
-      <c r="B42" s="535"/>
-      <c r="C42" s="535"/>
-      <c r="D42" s="535"/>
-      <c r="E42" s="535"/>
-      <c r="F42" s="580"/>
-      <c r="G42" s="543"/>
+    <row r="42" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A42" s="538"/>
+      <c r="B42" s="538"/>
+      <c r="C42" s="538"/>
+      <c r="D42" s="538"/>
+      <c r="E42" s="538"/>
+      <c r="F42" s="604"/>
+      <c r="G42" s="552"/>
       <c r="H42" s="225"/>
       <c r="I42" s="6"/>
       <c r="J42" s="145"/>
@@ -14745,26 +14769,26 @@
       <c r="HV42" s="6"/>
       <c r="HW42" s="6"/>
     </row>
-    <row r="43" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="536"/>
-      <c r="B43" s="536"/>
-      <c r="C43" s="536"/>
-      <c r="D43" s="536"/>
-      <c r="E43" s="536"/>
-      <c r="F43" s="581"/>
-      <c r="G43" s="564"/>
+    <row r="43" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="539"/>
+      <c r="B43" s="539"/>
+      <c r="C43" s="539"/>
+      <c r="D43" s="539"/>
+      <c r="E43" s="539"/>
+      <c r="F43" s="641"/>
+      <c r="G43" s="562"/>
       <c r="H43" s="385"/>
       <c r="I43" s="113"/>
-      <c r="J43" s="565"/>
-      <c r="K43" s="566"/>
+      <c r="J43" s="645"/>
+      <c r="K43" s="568"/>
       <c r="L43" s="114"/>
       <c r="M43" s="113"/>
       <c r="N43" s="113"/>
       <c r="O43" s="386"/>
       <c r="P43" s="387"/>
       <c r="Q43" s="386"/>
-      <c r="R43" s="558"/>
-      <c r="S43" s="559"/>
+      <c r="R43" s="634"/>
+      <c r="S43" s="635"/>
       <c r="T43" s="6"/>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
@@ -14978,16 +15002,16 @@
       <c r="HV43" s="6"/>
       <c r="HW43" s="6"/>
     </row>
-    <row r="44" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="537"/>
-      <c r="B44" s="554"/>
-      <c r="C44" s="554"/>
-      <c r="D44" s="554"/>
-      <c r="E44" s="554"/>
-      <c r="F44" s="597" t="s">
-        <v>31</v>
+    <row r="44" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A44" s="544"/>
+      <c r="B44" s="557"/>
+      <c r="C44" s="557"/>
+      <c r="D44" s="557"/>
+      <c r="E44" s="557"/>
+      <c r="F44" s="603" t="s">
+        <v>27</v>
       </c>
-      <c r="G44" s="589" t="s">
+      <c r="G44" s="587" t="s">
         <v>18</v>
       </c>
       <c r="H44" s="389"/>
@@ -14998,8 +15022,8 @@
       <c r="M44" s="233"/>
       <c r="N44" s="233"/>
       <c r="O44" s="234"/>
-      <c r="P44" s="633"/>
-      <c r="Q44" s="634"/>
+      <c r="P44" s="607"/>
+      <c r="Q44" s="608"/>
       <c r="R44" s="10"/>
       <c r="S44" s="10"/>
       <c r="T44" s="18"/>
@@ -15215,14 +15239,14 @@
       <c r="HV44" s="6"/>
       <c r="HW44" s="6"/>
     </row>
-    <row r="45" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="535"/>
-      <c r="B45" s="535"/>
-      <c r="C45" s="535"/>
-      <c r="D45" s="535"/>
-      <c r="E45" s="535"/>
-      <c r="F45" s="580"/>
-      <c r="G45" s="543"/>
+    <row r="45" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A45" s="538"/>
+      <c r="B45" s="538"/>
+      <c r="C45" s="538"/>
+      <c r="D45" s="538"/>
+      <c r="E45" s="538"/>
+      <c r="F45" s="604"/>
+      <c r="G45" s="552"/>
       <c r="H45" s="390"/>
       <c r="I45" s="61"/>
       <c r="J45" s="29"/>
@@ -15231,8 +15255,8 @@
       <c r="M45" s="391"/>
       <c r="N45" s="391"/>
       <c r="O45" s="392"/>
-      <c r="P45" s="562"/>
-      <c r="Q45" s="539"/>
+      <c r="P45" s="556"/>
+      <c r="Q45" s="541"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="27"/>
@@ -15448,14 +15472,14 @@
       <c r="HV45" s="6"/>
       <c r="HW45" s="6"/>
     </row>
-    <row r="46" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="536"/>
-      <c r="B46" s="536"/>
-      <c r="C46" s="536"/>
-      <c r="D46" s="536"/>
-      <c r="E46" s="536"/>
-      <c r="F46" s="580"/>
-      <c r="G46" s="544"/>
+    <row r="46" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A46" s="539"/>
+      <c r="B46" s="539"/>
+      <c r="C46" s="539"/>
+      <c r="D46" s="539"/>
+      <c r="E46" s="539"/>
+      <c r="F46" s="604"/>
+      <c r="G46" s="566"/>
       <c r="H46" s="393"/>
       <c r="I46" s="207"/>
       <c r="J46" s="52"/>
@@ -15464,8 +15488,8 @@
       <c r="M46" s="395"/>
       <c r="N46" s="395"/>
       <c r="O46" s="381"/>
-      <c r="P46" s="540"/>
-      <c r="Q46" s="539"/>
+      <c r="P46" s="577"/>
+      <c r="Q46" s="541"/>
       <c r="R46" s="197"/>
       <c r="S46" s="197"/>
       <c r="T46" s="27"/>
@@ -15681,22 +15705,22 @@
       <c r="HV46" s="6"/>
       <c r="HW46" s="6"/>
     </row>
-    <row r="47" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="553">
+    <row r="47" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A47" s="633">
         <v>9</v>
       </c>
-      <c r="B47" s="534">
+      <c r="B47" s="563">
         <v>8</v>
       </c>
-      <c r="C47" s="534">
+      <c r="C47" s="563">
         <v>5</v>
       </c>
-      <c r="D47" s="534">
+      <c r="D47" s="563">
         <v>3</v>
       </c>
-      <c r="E47" s="534"/>
-      <c r="F47" s="580"/>
-      <c r="G47" s="572" t="s">
+      <c r="E47" s="563"/>
+      <c r="F47" s="604"/>
+      <c r="G47" s="565" t="s">
         <v>19</v>
       </c>
       <c r="H47" s="258"/>
@@ -15707,8 +15731,8 @@
       <c r="M47" s="396"/>
       <c r="N47" s="396"/>
       <c r="O47" s="397"/>
-      <c r="P47" s="538"/>
-      <c r="Q47" s="539"/>
+      <c r="P47" s="576"/>
+      <c r="Q47" s="541"/>
       <c r="R47" s="6"/>
       <c r="S47" s="6"/>
       <c r="T47" s="398"/>
@@ -15924,14 +15948,14 @@
       <c r="HV47" s="6"/>
       <c r="HW47" s="6"/>
     </row>
-    <row r="48" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="535"/>
-      <c r="B48" s="535"/>
-      <c r="C48" s="535"/>
-      <c r="D48" s="535"/>
-      <c r="E48" s="535"/>
-      <c r="F48" s="580"/>
-      <c r="G48" s="543"/>
+    <row r="48" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A48" s="538"/>
+      <c r="B48" s="538"/>
+      <c r="C48" s="538"/>
+      <c r="D48" s="538"/>
+      <c r="E48" s="538"/>
+      <c r="F48" s="604"/>
+      <c r="G48" s="552"/>
       <c r="H48" s="265"/>
       <c r="I48" s="54"/>
       <c r="J48" s="54"/>
@@ -16157,14 +16181,14 @@
       <c r="HV48" s="6"/>
       <c r="HW48" s="6"/>
     </row>
-    <row r="49" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="536"/>
-      <c r="B49" s="536"/>
-      <c r="C49" s="536"/>
-      <c r="D49" s="536"/>
-      <c r="E49" s="536"/>
-      <c r="F49" s="580"/>
-      <c r="G49" s="544"/>
+    <row r="49" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A49" s="539"/>
+      <c r="B49" s="539"/>
+      <c r="C49" s="539"/>
+      <c r="D49" s="539"/>
+      <c r="E49" s="539"/>
+      <c r="F49" s="604"/>
+      <c r="G49" s="566"/>
       <c r="H49" s="305"/>
       <c r="I49" s="84"/>
       <c r="J49" s="70"/>
@@ -16173,8 +16197,8 @@
       <c r="M49" s="395"/>
       <c r="N49" s="395"/>
       <c r="O49" s="381"/>
-      <c r="P49" s="549"/>
-      <c r="Q49" s="539"/>
+      <c r="P49" s="593"/>
+      <c r="Q49" s="541"/>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
       <c r="T49" s="401"/>
@@ -16390,36 +16414,36 @@
       <c r="HV49" s="6"/>
       <c r="HW49" s="6"/>
     </row>
-    <row r="50" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="534">
+    <row r="50" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A50" s="563">
         <v>22</v>
       </c>
-      <c r="B50" s="534">
+      <c r="B50" s="563">
         <v>22</v>
       </c>
-      <c r="C50" s="534">
+      <c r="C50" s="563">
         <v>19</v>
       </c>
-      <c r="D50" s="534">
+      <c r="D50" s="563">
         <v>17</v>
       </c>
-      <c r="E50" s="552"/>
-      <c r="F50" s="580"/>
-      <c r="G50" s="587" t="s">
+      <c r="E50" s="537"/>
+      <c r="F50" s="604"/>
+      <c r="G50" s="601" t="s">
         <v>20</v>
       </c>
-      <c r="H50" s="557"/>
-      <c r="I50" s="546"/>
-      <c r="J50" s="546"/>
-      <c r="K50" s="547"/>
-      <c r="L50" s="557"/>
-      <c r="M50" s="547"/>
-      <c r="N50" s="545"/>
-      <c r="O50" s="547"/>
+      <c r="H50" s="584"/>
+      <c r="I50" s="549"/>
+      <c r="J50" s="549"/>
+      <c r="K50" s="580"/>
+      <c r="L50" s="584"/>
+      <c r="M50" s="580"/>
+      <c r="N50" s="579"/>
+      <c r="O50" s="580"/>
       <c r="P50" s="142"/>
       <c r="Q50" s="184"/>
-      <c r="R50" s="548"/>
-      <c r="S50" s="546"/>
+      <c r="R50" s="649"/>
+      <c r="S50" s="549"/>
       <c r="T50" s="57"/>
       <c r="U50" s="58"/>
       <c r="V50" s="58"/>
@@ -16432,10 +16456,10 @@
       <c r="AC50" s="10"/>
       <c r="AD50" s="10"/>
       <c r="AE50" s="45"/>
-      <c r="AF50" s="545"/>
-      <c r="AG50" s="546"/>
-      <c r="AH50" s="546"/>
-      <c r="AI50" s="547"/>
+      <c r="AF50" s="579"/>
+      <c r="AG50" s="549"/>
+      <c r="AH50" s="549"/>
+      <c r="AI50" s="580"/>
       <c r="AJ50" s="6"/>
       <c r="AK50" s="153"/>
       <c r="AL50" s="153"/>
@@ -16633,26 +16657,26 @@
       <c r="HV50" s="6"/>
       <c r="HW50" s="6"/>
     </row>
-    <row r="51" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A51" s="535"/>
-      <c r="B51" s="535"/>
-      <c r="C51" s="535"/>
-      <c r="D51" s="535"/>
-      <c r="E51" s="535"/>
-      <c r="F51" s="580"/>
-      <c r="G51" s="543"/>
+    <row r="51" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A51" s="538"/>
+      <c r="B51" s="538"/>
+      <c r="C51" s="538"/>
+      <c r="D51" s="538"/>
+      <c r="E51" s="538"/>
+      <c r="F51" s="604"/>
+      <c r="G51" s="552"/>
       <c r="H51" s="404"/>
       <c r="I51" s="82"/>
       <c r="J51" s="82"/>
       <c r="K51" s="217"/>
-      <c r="L51" s="582"/>
-      <c r="M51" s="539"/>
-      <c r="N51" s="593"/>
-      <c r="O51" s="539"/>
+      <c r="L51" s="573"/>
+      <c r="M51" s="541"/>
+      <c r="N51" s="545"/>
+      <c r="O51" s="541"/>
       <c r="P51" s="6"/>
       <c r="Q51" s="151"/>
-      <c r="R51" s="625"/>
-      <c r="S51" s="551"/>
+      <c r="R51" s="609"/>
+      <c r="S51" s="543"/>
       <c r="T51" s="60"/>
       <c r="U51" s="61"/>
       <c r="V51" s="61"/>
@@ -16666,8 +16690,8 @@
       <c r="AD51" s="10"/>
       <c r="AE51" s="45"/>
       <c r="AF51" s="405"/>
-      <c r="AG51" s="606"/>
-      <c r="AH51" s="551"/>
+      <c r="AG51" s="651"/>
+      <c r="AH51" s="543"/>
       <c r="AI51" s="406"/>
       <c r="AJ51" s="6"/>
       <c r="AK51" s="86"/>
@@ -16866,26 +16890,26 @@
       <c r="HV51" s="6"/>
       <c r="HW51" s="6"/>
     </row>
-    <row r="52" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="536"/>
-      <c r="B52" s="536"/>
-      <c r="C52" s="536"/>
-      <c r="D52" s="536"/>
-      <c r="E52" s="536"/>
-      <c r="F52" s="580"/>
-      <c r="G52" s="588"/>
+    <row r="52" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A52" s="539"/>
+      <c r="B52" s="539"/>
+      <c r="C52" s="539"/>
+      <c r="D52" s="539"/>
+      <c r="E52" s="539"/>
+      <c r="F52" s="604"/>
+      <c r="G52" s="602"/>
       <c r="H52" s="407"/>
       <c r="I52" s="192"/>
       <c r="J52" s="192"/>
       <c r="K52" s="367"/>
-      <c r="L52" s="590"/>
-      <c r="M52" s="539"/>
-      <c r="N52" s="540"/>
-      <c r="O52" s="539"/>
+      <c r="L52" s="581"/>
+      <c r="M52" s="541"/>
+      <c r="N52" s="577"/>
+      <c r="O52" s="541"/>
       <c r="P52" s="149"/>
       <c r="Q52" s="215"/>
-      <c r="R52" s="600"/>
-      <c r="S52" s="551"/>
+      <c r="R52" s="542"/>
+      <c r="S52" s="543"/>
       <c r="T52" s="249"/>
       <c r="U52" s="73"/>
       <c r="V52" s="73"/>
@@ -17099,38 +17123,38 @@
       <c r="HV52" s="6"/>
       <c r="HW52" s="6"/>
     </row>
-    <row r="53" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="552">
+    <row r="53" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A53" s="537">
         <v>0</v>
       </c>
-      <c r="B53" s="552">
+      <c r="B53" s="537">
         <v>0</v>
       </c>
-      <c r="C53" s="552">
+      <c r="C53" s="537">
         <v>0</v>
       </c>
-      <c r="D53" s="534">
+      <c r="D53" s="563">
         <v>31</v>
       </c>
-      <c r="E53" s="552">
+      <c r="E53" s="537">
         <v>0</v>
       </c>
-      <c r="F53" s="580"/>
-      <c r="G53" s="568" t="s">
-        <v>23</v>
+      <c r="F53" s="604"/>
+      <c r="G53" s="647" t="s">
+        <v>22</v>
       </c>
-      <c r="H53" s="592"/>
-      <c r="I53" s="551"/>
-      <c r="J53" s="551"/>
-      <c r="K53" s="539"/>
-      <c r="L53" s="541"/>
-      <c r="M53" s="539"/>
-      <c r="N53" s="538"/>
-      <c r="O53" s="539"/>
+      <c r="H53" s="555"/>
+      <c r="I53" s="543"/>
+      <c r="J53" s="543"/>
+      <c r="K53" s="541"/>
+      <c r="L53" s="599"/>
+      <c r="M53" s="541"/>
+      <c r="N53" s="576"/>
+      <c r="O53" s="541"/>
       <c r="P53" s="6"/>
       <c r="Q53" s="151"/>
-      <c r="R53" s="627"/>
-      <c r="S53" s="551"/>
+      <c r="R53" s="610"/>
+      <c r="S53" s="543"/>
       <c r="T53" s="369"/>
       <c r="U53" s="370"/>
       <c r="V53" s="79"/>
@@ -17140,13 +17164,13 @@
       <c r="Z53" s="79"/>
       <c r="AA53" s="79"/>
       <c r="AB53" s="574"/>
-      <c r="AC53" s="575"/>
-      <c r="AD53" s="575"/>
-      <c r="AE53" s="576"/>
-      <c r="AF53" s="583"/>
-      <c r="AG53" s="551"/>
-      <c r="AH53" s="551"/>
-      <c r="AI53" s="539"/>
+      <c r="AC53" s="535"/>
+      <c r="AD53" s="535"/>
+      <c r="AE53" s="547"/>
+      <c r="AF53" s="642"/>
+      <c r="AG53" s="543"/>
+      <c r="AH53" s="543"/>
+      <c r="AI53" s="541"/>
       <c r="AJ53" s="3"/>
       <c r="AK53" s="153"/>
       <c r="AL53" s="153"/>
@@ -17344,14 +17368,14 @@
       <c r="HV53" s="6"/>
       <c r="HW53" s="6"/>
     </row>
-    <row r="54" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="535"/>
-      <c r="B54" s="535"/>
-      <c r="C54" s="535"/>
-      <c r="D54" s="535"/>
-      <c r="E54" s="535"/>
-      <c r="F54" s="580"/>
-      <c r="G54" s="543"/>
+    <row r="54" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A54" s="538"/>
+      <c r="B54" s="538"/>
+      <c r="C54" s="538"/>
+      <c r="D54" s="538"/>
+      <c r="E54" s="538"/>
+      <c r="F54" s="604"/>
+      <c r="G54" s="552"/>
       <c r="H54" s="404"/>
       <c r="I54" s="82"/>
       <c r="J54" s="82"/>
@@ -17577,26 +17601,26 @@
       <c r="HV54" s="6"/>
       <c r="HW54" s="6"/>
     </row>
-    <row r="55" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="536"/>
-      <c r="B55" s="536"/>
-      <c r="C55" s="536"/>
-      <c r="D55" s="536"/>
-      <c r="E55" s="536"/>
-      <c r="F55" s="580"/>
-      <c r="G55" s="569"/>
+    <row r="55" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A55" s="539"/>
+      <c r="B55" s="539"/>
+      <c r="C55" s="539"/>
+      <c r="D55" s="539"/>
+      <c r="E55" s="539"/>
+      <c r="F55" s="604"/>
+      <c r="G55" s="648"/>
       <c r="H55" s="409"/>
       <c r="I55" s="137"/>
       <c r="J55" s="88"/>
       <c r="K55" s="160"/>
-      <c r="L55" s="607"/>
-      <c r="M55" s="539"/>
-      <c r="N55" s="651"/>
-      <c r="O55" s="539"/>
+      <c r="L55" s="629"/>
+      <c r="M55" s="541"/>
+      <c r="N55" s="540"/>
+      <c r="O55" s="541"/>
       <c r="P55" s="197"/>
       <c r="Q55" s="104"/>
-      <c r="R55" s="549"/>
-      <c r="S55" s="539"/>
+      <c r="R55" s="593"/>
+      <c r="S55" s="541"/>
       <c r="T55" s="374"/>
       <c r="U55" s="375"/>
       <c r="V55" s="375"/>
@@ -17810,15 +17834,15 @@
       <c r="HV55" s="6"/>
       <c r="HW55" s="6"/>
     </row>
-    <row r="56" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="537"/>
-      <c r="B56" s="537"/>
-      <c r="C56" s="537"/>
-      <c r="D56" s="537"/>
-      <c r="E56" s="537"/>
-      <c r="F56" s="580"/>
-      <c r="G56" s="572" t="s">
-        <v>25</v>
+    <row r="56" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A56" s="544"/>
+      <c r="B56" s="544"/>
+      <c r="C56" s="544"/>
+      <c r="D56" s="544"/>
+      <c r="E56" s="544"/>
+      <c r="F56" s="604"/>
+      <c r="G56" s="565" t="s">
+        <v>24</v>
       </c>
       <c r="H56" s="358"/>
       <c r="I56" s="106"/>
@@ -17826,8 +17850,8 @@
       <c r="K56" s="186"/>
       <c r="L56" s="384"/>
       <c r="M56" s="143"/>
-      <c r="N56" s="545"/>
-      <c r="O56" s="547"/>
+      <c r="N56" s="579"/>
+      <c r="O56" s="580"/>
       <c r="P56" s="412"/>
       <c r="Q56" s="412"/>
       <c r="R56" s="412"/>
@@ -17840,10 +17864,10 @@
       <c r="Y56" s="82"/>
       <c r="Z56" s="82"/>
       <c r="AA56" s="226"/>
-      <c r="AB56" s="570"/>
-      <c r="AC56" s="551"/>
-      <c r="AD56" s="551"/>
-      <c r="AE56" s="539"/>
+      <c r="AB56" s="592"/>
+      <c r="AC56" s="543"/>
+      <c r="AD56" s="543"/>
+      <c r="AE56" s="541"/>
       <c r="AF56" s="37"/>
       <c r="AG56" s="37"/>
       <c r="AH56" s="37"/>
@@ -18045,22 +18069,22 @@
       <c r="HV56" s="6"/>
       <c r="HW56" s="6"/>
     </row>
-    <row r="57" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A57" s="535"/>
-      <c r="B57" s="535"/>
-      <c r="C57" s="535"/>
-      <c r="D57" s="535"/>
-      <c r="E57" s="535"/>
-      <c r="F57" s="580"/>
-      <c r="G57" s="543"/>
+    <row r="57" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A57" s="538"/>
+      <c r="B57" s="538"/>
+      <c r="C57" s="538"/>
+      <c r="D57" s="538"/>
+      <c r="E57" s="538"/>
+      <c r="F57" s="604"/>
+      <c r="G57" s="552"/>
       <c r="H57" s="169"/>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
       <c r="K57" s="168"/>
       <c r="L57" s="225"/>
       <c r="M57" s="146"/>
-      <c r="N57" s="593"/>
-      <c r="O57" s="539"/>
+      <c r="N57" s="545"/>
+      <c r="O57" s="541"/>
       <c r="P57" s="158"/>
       <c r="Q57" s="158"/>
       <c r="R57" s="158"/>
@@ -18278,22 +18302,22 @@
       <c r="HV57" s="6"/>
       <c r="HW57" s="6"/>
     </row>
-    <row r="58" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="536"/>
-      <c r="B58" s="536"/>
-      <c r="C58" s="536"/>
-      <c r="D58" s="536"/>
-      <c r="E58" s="536"/>
-      <c r="F58" s="580"/>
-      <c r="G58" s="544"/>
+    <row r="58" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A58" s="539"/>
+      <c r="B58" s="539"/>
+      <c r="C58" s="539"/>
+      <c r="D58" s="539"/>
+      <c r="E58" s="539"/>
+      <c r="F58" s="604"/>
+      <c r="G58" s="566"/>
       <c r="H58" s="332"/>
       <c r="I58" s="89"/>
       <c r="J58" s="89"/>
       <c r="K58" s="194"/>
       <c r="L58" s="333"/>
       <c r="M58" s="334"/>
-      <c r="N58" s="540"/>
-      <c r="O58" s="539"/>
+      <c r="N58" s="577"/>
+      <c r="O58" s="541"/>
       <c r="P58" s="335"/>
       <c r="Q58" s="335"/>
       <c r="R58" s="161"/>
@@ -18511,15 +18535,15 @@
       <c r="HV58" s="6"/>
       <c r="HW58" s="6"/>
     </row>
-    <row r="59" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="537"/>
-      <c r="B59" s="537"/>
-      <c r="C59" s="537"/>
-      <c r="D59" s="537"/>
-      <c r="E59" s="537"/>
-      <c r="F59" s="580"/>
-      <c r="G59" s="602" t="s">
-        <v>27</v>
+    <row r="59" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A59" s="544"/>
+      <c r="B59" s="544"/>
+      <c r="C59" s="544"/>
+      <c r="D59" s="544"/>
+      <c r="E59" s="544"/>
+      <c r="F59" s="604"/>
+      <c r="G59" s="561" t="s">
+        <v>25</v>
       </c>
       <c r="H59" s="169"/>
       <c r="I59" s="26"/>
@@ -18527,8 +18551,8 @@
       <c r="K59" s="168"/>
       <c r="L59" s="225"/>
       <c r="M59" s="146"/>
-      <c r="N59" s="538"/>
-      <c r="O59" s="539"/>
+      <c r="N59" s="576"/>
+      <c r="O59" s="541"/>
       <c r="P59" s="82"/>
       <c r="Q59" s="82"/>
       <c r="R59" s="82"/>
@@ -18746,14 +18770,14 @@
       <c r="HV59" s="6"/>
       <c r="HW59" s="6"/>
     </row>
-    <row r="60" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="535"/>
-      <c r="B60" s="535"/>
-      <c r="C60" s="535"/>
-      <c r="D60" s="535"/>
-      <c r="E60" s="535"/>
-      <c r="F60" s="580"/>
-      <c r="G60" s="543"/>
+    <row r="60" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A60" s="538"/>
+      <c r="B60" s="538"/>
+      <c r="C60" s="538"/>
+      <c r="D60" s="538"/>
+      <c r="E60" s="538"/>
+      <c r="F60" s="604"/>
+      <c r="G60" s="552"/>
       <c r="H60" s="169"/>
       <c r="I60" s="26"/>
       <c r="J60" s="26"/>
@@ -18979,22 +19003,22 @@
       <c r="HV60" s="6"/>
       <c r="HW60" s="6"/>
     </row>
-    <row r="61" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="536"/>
-      <c r="B61" s="536"/>
-      <c r="C61" s="536"/>
-      <c r="D61" s="536"/>
-      <c r="E61" s="536"/>
-      <c r="F61" s="580"/>
-      <c r="G61" s="564"/>
+    <row r="61" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A61" s="539"/>
+      <c r="B61" s="539"/>
+      <c r="C61" s="539"/>
+      <c r="D61" s="539"/>
+      <c r="E61" s="539"/>
+      <c r="F61" s="604"/>
+      <c r="G61" s="562"/>
       <c r="H61" s="169"/>
       <c r="I61" s="26"/>
       <c r="J61" s="26"/>
       <c r="K61" s="168"/>
       <c r="L61" s="419"/>
       <c r="M61" s="420"/>
-      <c r="N61" s="549"/>
-      <c r="O61" s="539"/>
+      <c r="N61" s="593"/>
+      <c r="O61" s="541"/>
       <c r="P61" s="197"/>
       <c r="Q61" s="197"/>
       <c r="R61" s="197"/>
@@ -19212,16 +19236,16 @@
       <c r="HV61" s="6"/>
       <c r="HW61" s="6"/>
     </row>
-    <row r="62" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="537"/>
-      <c r="B62" s="554"/>
-      <c r="C62" s="554"/>
-      <c r="D62" s="554"/>
-      <c r="E62" s="644"/>
-      <c r="F62" s="584" t="s">
-        <v>32</v>
+    <row r="62" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="544"/>
+      <c r="B62" s="557"/>
+      <c r="C62" s="557"/>
+      <c r="D62" s="557"/>
+      <c r="E62" s="586"/>
+      <c r="F62" s="643" t="s">
+        <v>28</v>
       </c>
-      <c r="G62" s="598" t="s">
+      <c r="G62" s="606" t="s">
         <v>18</v>
       </c>
       <c r="H62" s="285"/>
@@ -19449,14 +19473,14 @@
       <c r="HV62" s="6"/>
       <c r="HW62" s="6"/>
     </row>
-    <row r="63" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="535"/>
-      <c r="B63" s="535"/>
-      <c r="C63" s="535"/>
-      <c r="D63" s="535"/>
-      <c r="E63" s="535"/>
-      <c r="F63" s="580"/>
-      <c r="G63" s="543"/>
+    <row r="63" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="538"/>
+      <c r="B63" s="538"/>
+      <c r="C63" s="538"/>
+      <c r="D63" s="538"/>
+      <c r="E63" s="538"/>
+      <c r="F63" s="604"/>
+      <c r="G63" s="552"/>
       <c r="H63" s="272"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
@@ -19682,14 +19706,14 @@
       <c r="HV63" s="6"/>
       <c r="HW63" s="6"/>
     </row>
-    <row r="64" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A64" s="536"/>
-      <c r="B64" s="536"/>
-      <c r="C64" s="536"/>
-      <c r="D64" s="536"/>
-      <c r="E64" s="536"/>
-      <c r="F64" s="580"/>
-      <c r="G64" s="543"/>
+    <row r="64" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A64" s="539"/>
+      <c r="B64" s="539"/>
+      <c r="C64" s="539"/>
+      <c r="D64" s="539"/>
+      <c r="E64" s="539"/>
+      <c r="F64" s="604"/>
+      <c r="G64" s="552"/>
       <c r="H64" s="204"/>
       <c r="I64" s="32"/>
       <c r="J64" s="32"/>
@@ -19915,24 +19939,24 @@
       <c r="HV64" s="6"/>
       <c r="HW64" s="6"/>
     </row>
-    <row r="65" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="534">
+    <row r="65" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A65" s="563">
         <v>9</v>
       </c>
-      <c r="B65" s="534">
+      <c r="B65" s="563">
         <v>9</v>
       </c>
-      <c r="C65" s="534">
+      <c r="C65" s="563">
         <v>6</v>
       </c>
-      <c r="D65" s="534">
+      <c r="D65" s="563">
         <v>4</v>
       </c>
-      <c r="E65" s="534">
+      <c r="E65" s="563">
         <v>1</v>
       </c>
-      <c r="F65" s="580"/>
-      <c r="G65" s="572" t="s">
+      <c r="F65" s="604"/>
+      <c r="G65" s="565" t="s">
         <v>19</v>
       </c>
       <c r="H65" s="358"/>
@@ -19955,10 +19979,10 @@
       <c r="Y65" s="106"/>
       <c r="Z65" s="106"/>
       <c r="AA65" s="132"/>
-      <c r="AB65" s="647"/>
-      <c r="AC65" s="546"/>
-      <c r="AD65" s="546"/>
-      <c r="AE65" s="648"/>
+      <c r="AB65" s="548"/>
+      <c r="AC65" s="549"/>
+      <c r="AD65" s="549"/>
+      <c r="AE65" s="550"/>
       <c r="AF65" s="43"/>
       <c r="AG65" s="10"/>
       <c r="AH65" s="10"/>
@@ -20160,14 +20184,14 @@
       <c r="HV65" s="6"/>
       <c r="HW65" s="6"/>
     </row>
-    <row r="66" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="535"/>
-      <c r="B66" s="535"/>
-      <c r="C66" s="535"/>
-      <c r="D66" s="535"/>
-      <c r="E66" s="535"/>
-      <c r="F66" s="580"/>
-      <c r="G66" s="543"/>
+    <row r="66" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A66" s="538"/>
+      <c r="B66" s="538"/>
+      <c r="C66" s="538"/>
+      <c r="D66" s="538"/>
+      <c r="E66" s="538"/>
+      <c r="F66" s="604"/>
+      <c r="G66" s="552"/>
       <c r="H66" s="169"/>
       <c r="I66" s="26"/>
       <c r="J66" s="26"/>
@@ -20393,14 +20417,14 @@
       <c r="HV66" s="6"/>
       <c r="HW66" s="6"/>
     </row>
-    <row r="67" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="536"/>
-      <c r="B67" s="536"/>
-      <c r="C67" s="536"/>
-      <c r="D67" s="536"/>
-      <c r="E67" s="536"/>
-      <c r="F67" s="580"/>
-      <c r="G67" s="544"/>
+    <row r="67" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A67" s="539"/>
+      <c r="B67" s="539"/>
+      <c r="C67" s="539"/>
+      <c r="D67" s="539"/>
+      <c r="E67" s="539"/>
+      <c r="F67" s="604"/>
+      <c r="G67" s="566"/>
       <c r="H67" s="332"/>
       <c r="I67" s="89"/>
       <c r="J67" s="89"/>
@@ -20627,27 +20651,27 @@
       <c r="HW67" s="6"/>
     </row>
     <row r="68" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="534">
+      <c r="A68" s="563">
         <v>23</v>
       </c>
-      <c r="B68" s="534">
+      <c r="B68" s="563">
         <v>23</v>
       </c>
-      <c r="C68" s="534">
+      <c r="C68" s="563">
         <v>20</v>
       </c>
-      <c r="D68" s="534">
+      <c r="D68" s="563">
         <v>18</v>
       </c>
-      <c r="E68" s="534"/>
-      <c r="F68" s="580"/>
-      <c r="G68" s="631" t="s">
+      <c r="E68" s="563"/>
+      <c r="F68" s="604"/>
+      <c r="G68" s="594" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="557"/>
-      <c r="I68" s="546"/>
-      <c r="J68" s="546"/>
-      <c r="K68" s="547"/>
+      <c r="H68" s="584"/>
+      <c r="I68" s="549"/>
+      <c r="J68" s="549"/>
+      <c r="K68" s="580"/>
       <c r="L68" s="258"/>
       <c r="M68" s="58"/>
       <c r="N68" s="26"/>
@@ -20664,14 +20688,14 @@
       <c r="Y68" s="26"/>
       <c r="Z68" s="26"/>
       <c r="AA68" s="28"/>
-      <c r="AB68" s="638"/>
-      <c r="AC68" s="575"/>
-      <c r="AD68" s="575"/>
-      <c r="AE68" s="639"/>
-      <c r="AF68" s="555"/>
-      <c r="AG68" s="546"/>
-      <c r="AH68" s="546"/>
-      <c r="AI68" s="547"/>
+      <c r="AB68" s="534"/>
+      <c r="AC68" s="535"/>
+      <c r="AD68" s="535"/>
+      <c r="AE68" s="536"/>
+      <c r="AF68" s="591"/>
+      <c r="AG68" s="549"/>
+      <c r="AH68" s="549"/>
+      <c r="AI68" s="580"/>
       <c r="AJ68" s="122"/>
       <c r="AK68" s="6"/>
       <c r="AL68" s="6"/>
@@ -20869,14 +20893,14 @@
       <c r="HV68" s="6"/>
       <c r="HW68" s="6"/>
     </row>
-    <row r="69" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A69" s="535"/>
-      <c r="B69" s="535"/>
-      <c r="C69" s="535"/>
-      <c r="D69" s="535"/>
-      <c r="E69" s="535"/>
-      <c r="F69" s="580"/>
-      <c r="G69" s="543"/>
+    <row r="69" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A69" s="538"/>
+      <c r="B69" s="538"/>
+      <c r="C69" s="538"/>
+      <c r="D69" s="538"/>
+      <c r="E69" s="538"/>
+      <c r="F69" s="604"/>
+      <c r="G69" s="552"/>
       <c r="H69" s="404"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
@@ -21102,14 +21126,14 @@
       <c r="HV69" s="6"/>
       <c r="HW69" s="6"/>
     </row>
-    <row r="70" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="536"/>
-      <c r="B70" s="536"/>
-      <c r="C70" s="536"/>
-      <c r="D70" s="536"/>
-      <c r="E70" s="536"/>
-      <c r="F70" s="580"/>
-      <c r="G70" s="632"/>
+    <row r="70" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A70" s="539"/>
+      <c r="B70" s="539"/>
+      <c r="C70" s="539"/>
+      <c r="D70" s="539"/>
+      <c r="E70" s="539"/>
+      <c r="F70" s="604"/>
+      <c r="G70" s="553"/>
       <c r="H70" s="407"/>
       <c r="I70" s="192"/>
       <c r="J70" s="192"/>
@@ -21336,37 +21360,37 @@
       <c r="HW70" s="6"/>
     </row>
     <row r="71" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="552">
+      <c r="A71" s="537">
         <v>0</v>
       </c>
-      <c r="B71" s="552">
+      <c r="B71" s="537">
         <v>0</v>
       </c>
-      <c r="C71" s="552">
+      <c r="C71" s="537">
         <v>0</v>
       </c>
-      <c r="D71" s="552">
+      <c r="D71" s="537">
         <v>0</v>
       </c>
-      <c r="E71" s="534">
+      <c r="E71" s="563">
         <v>0</v>
       </c>
-      <c r="F71" s="580"/>
-      <c r="G71" s="542" t="s">
-        <v>23</v>
+      <c r="F71" s="604"/>
+      <c r="G71" s="595" t="s">
+        <v>22</v>
       </c>
-      <c r="H71" s="629"/>
-      <c r="I71" s="575"/>
-      <c r="J71" s="575"/>
-      <c r="K71" s="576"/>
-      <c r="L71" s="629"/>
-      <c r="M71" s="575"/>
-      <c r="N71" s="575"/>
-      <c r="O71" s="576"/>
-      <c r="P71" s="635"/>
-      <c r="Q71" s="575"/>
-      <c r="R71" s="575"/>
-      <c r="S71" s="576"/>
+      <c r="H71" s="546"/>
+      <c r="I71" s="535"/>
+      <c r="J71" s="535"/>
+      <c r="K71" s="547"/>
+      <c r="L71" s="546"/>
+      <c r="M71" s="535"/>
+      <c r="N71" s="535"/>
+      <c r="O71" s="547"/>
+      <c r="P71" s="598"/>
+      <c r="Q71" s="535"/>
+      <c r="R71" s="535"/>
+      <c r="S71" s="547"/>
       <c r="T71" s="243"/>
       <c r="U71" s="244"/>
       <c r="V71" s="244"/>
@@ -21375,14 +21399,14 @@
       <c r="Y71" s="244"/>
       <c r="Z71" s="244"/>
       <c r="AA71" s="434"/>
-      <c r="AB71" s="571"/>
-      <c r="AC71" s="551"/>
-      <c r="AD71" s="551"/>
-      <c r="AE71" s="551"/>
-      <c r="AF71" s="570"/>
-      <c r="AG71" s="551"/>
-      <c r="AH71" s="551"/>
-      <c r="AI71" s="539"/>
+      <c r="AB71" s="622"/>
+      <c r="AC71" s="543"/>
+      <c r="AD71" s="543"/>
+      <c r="AE71" s="543"/>
+      <c r="AF71" s="592"/>
+      <c r="AG71" s="543"/>
+      <c r="AH71" s="543"/>
+      <c r="AI71" s="541"/>
       <c r="AJ71" s="122"/>
       <c r="AK71" s="6"/>
       <c r="AL71" s="6"/>
@@ -21580,14 +21604,14 @@
       <c r="HV71" s="6"/>
       <c r="HW71" s="6"/>
     </row>
-    <row r="72" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="535"/>
-      <c r="B72" s="535"/>
-      <c r="C72" s="535"/>
-      <c r="D72" s="535"/>
-      <c r="E72" s="535"/>
-      <c r="F72" s="580"/>
-      <c r="G72" s="543"/>
+    <row r="72" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A72" s="538"/>
+      <c r="B72" s="538"/>
+      <c r="C72" s="538"/>
+      <c r="D72" s="538"/>
+      <c r="E72" s="538"/>
+      <c r="F72" s="604"/>
+      <c r="G72" s="552"/>
       <c r="H72" s="404"/>
       <c r="I72" s="82"/>
       <c r="J72" s="82"/>
@@ -21813,14 +21837,14 @@
       <c r="HV72" s="6"/>
       <c r="HW72" s="6"/>
     </row>
-    <row r="73" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="536"/>
-      <c r="B73" s="536"/>
-      <c r="C73" s="536"/>
-      <c r="D73" s="536"/>
-      <c r="E73" s="536"/>
-      <c r="F73" s="580"/>
-      <c r="G73" s="544"/>
+    <row r="73" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A73" s="539"/>
+      <c r="B73" s="539"/>
+      <c r="C73" s="539"/>
+      <c r="D73" s="539"/>
+      <c r="E73" s="539"/>
+      <c r="F73" s="604"/>
+      <c r="G73" s="566"/>
       <c r="H73" s="251"/>
       <c r="I73" s="96"/>
       <c r="J73" s="96"/>
@@ -22046,40 +22070,40 @@
       <c r="HV73" s="6"/>
       <c r="HW73" s="6"/>
     </row>
-    <row r="74" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="537"/>
-      <c r="B74" s="537"/>
-      <c r="C74" s="537"/>
-      <c r="D74" s="537"/>
-      <c r="E74" s="612"/>
-      <c r="F74" s="580"/>
-      <c r="G74" s="589" t="s">
-        <v>25</v>
+    <row r="74" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A74" s="544"/>
+      <c r="B74" s="544"/>
+      <c r="C74" s="544"/>
+      <c r="D74" s="544"/>
+      <c r="E74" s="614"/>
+      <c r="F74" s="604"/>
+      <c r="G74" s="587" t="s">
+        <v>24</v>
       </c>
       <c r="H74" s="225"/>
       <c r="I74" s="6"/>
-      <c r="J74" s="570"/>
-      <c r="K74" s="539"/>
-      <c r="L74" s="570"/>
-      <c r="M74" s="551"/>
-      <c r="N74" s="551"/>
-      <c r="O74" s="551"/>
-      <c r="P74" s="551"/>
-      <c r="Q74" s="551"/>
-      <c r="R74" s="551"/>
-      <c r="S74" s="539"/>
-      <c r="T74" s="555"/>
-      <c r="U74" s="546"/>
-      <c r="V74" s="546"/>
-      <c r="W74" s="547"/>
-      <c r="X74" s="555"/>
-      <c r="Y74" s="546"/>
-      <c r="Z74" s="546"/>
-      <c r="AA74" s="547"/>
-      <c r="AB74" s="591"/>
-      <c r="AC74" s="546"/>
-      <c r="AD74" s="546"/>
-      <c r="AE74" s="546"/>
+      <c r="J74" s="592"/>
+      <c r="K74" s="541"/>
+      <c r="L74" s="592"/>
+      <c r="M74" s="543"/>
+      <c r="N74" s="543"/>
+      <c r="O74" s="543"/>
+      <c r="P74" s="543"/>
+      <c r="Q74" s="543"/>
+      <c r="R74" s="543"/>
+      <c r="S74" s="541"/>
+      <c r="T74" s="591"/>
+      <c r="U74" s="549"/>
+      <c r="V74" s="549"/>
+      <c r="W74" s="580"/>
+      <c r="X74" s="591"/>
+      <c r="Y74" s="549"/>
+      <c r="Z74" s="549"/>
+      <c r="AA74" s="580"/>
+      <c r="AB74" s="564"/>
+      <c r="AC74" s="549"/>
+      <c r="AD74" s="549"/>
+      <c r="AE74" s="549"/>
       <c r="AF74" s="145"/>
       <c r="AG74" s="6"/>
       <c r="AH74" s="6"/>
@@ -22281,34 +22305,34 @@
       <c r="HV74" s="6"/>
       <c r="HW74" s="6"/>
     </row>
-    <row r="75" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A75" s="535"/>
-      <c r="B75" s="535"/>
-      <c r="C75" s="535"/>
-      <c r="D75" s="535"/>
-      <c r="E75" s="535"/>
-      <c r="F75" s="580"/>
-      <c r="G75" s="543"/>
+    <row r="75" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A75" s="538"/>
+      <c r="B75" s="538"/>
+      <c r="C75" s="538"/>
+      <c r="D75" s="538"/>
+      <c r="E75" s="538"/>
+      <c r="F75" s="604"/>
+      <c r="G75" s="552"/>
       <c r="H75" s="225"/>
       <c r="I75" s="6"/>
-      <c r="J75" s="562"/>
-      <c r="K75" s="539"/>
-      <c r="L75" s="543"/>
-      <c r="M75" s="551"/>
-      <c r="N75" s="551"/>
-      <c r="O75" s="551"/>
-      <c r="P75" s="551"/>
-      <c r="Q75" s="551"/>
-      <c r="R75" s="551"/>
-      <c r="S75" s="539"/>
-      <c r="T75" s="562"/>
-      <c r="U75" s="551"/>
-      <c r="V75" s="551"/>
-      <c r="W75" s="539"/>
-      <c r="X75" s="562"/>
-      <c r="Y75" s="551"/>
-      <c r="Z75" s="551"/>
-      <c r="AA75" s="539"/>
+      <c r="J75" s="556"/>
+      <c r="K75" s="541"/>
+      <c r="L75" s="552"/>
+      <c r="M75" s="543"/>
+      <c r="N75" s="543"/>
+      <c r="O75" s="543"/>
+      <c r="P75" s="543"/>
+      <c r="Q75" s="543"/>
+      <c r="R75" s="543"/>
+      <c r="S75" s="541"/>
+      <c r="T75" s="556"/>
+      <c r="U75" s="543"/>
+      <c r="V75" s="543"/>
+      <c r="W75" s="541"/>
+      <c r="X75" s="556"/>
+      <c r="Y75" s="543"/>
+      <c r="Z75" s="543"/>
+      <c r="AA75" s="541"/>
       <c r="AB75" s="64"/>
       <c r="AC75" s="65"/>
       <c r="AD75" s="65"/>
@@ -22514,18 +22538,18 @@
       <c r="HV75" s="6"/>
       <c r="HW75" s="6"/>
     </row>
-    <row r="76" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="536"/>
-      <c r="B76" s="536"/>
-      <c r="C76" s="536"/>
-      <c r="D76" s="536"/>
-      <c r="E76" s="536"/>
-      <c r="F76" s="580"/>
-      <c r="G76" s="544"/>
+    <row r="76" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A76" s="539"/>
+      <c r="B76" s="539"/>
+      <c r="C76" s="539"/>
+      <c r="D76" s="539"/>
+      <c r="E76" s="539"/>
+      <c r="F76" s="604"/>
+      <c r="G76" s="566"/>
       <c r="H76" s="333"/>
       <c r="I76" s="197"/>
-      <c r="J76" s="573"/>
-      <c r="K76" s="539"/>
+      <c r="J76" s="554"/>
+      <c r="K76" s="541"/>
       <c r="L76" s="87"/>
       <c r="M76" s="96"/>
       <c r="N76" s="96"/>
@@ -22535,12 +22559,12 @@
       <c r="R76" s="197"/>
       <c r="S76" s="97"/>
       <c r="T76" s="227"/>
-      <c r="U76" s="600"/>
-      <c r="V76" s="551"/>
+      <c r="U76" s="542"/>
+      <c r="V76" s="543"/>
       <c r="W76" s="228"/>
       <c r="X76" s="229"/>
-      <c r="Y76" s="600"/>
-      <c r="Z76" s="551"/>
+      <c r="Y76" s="542"/>
+      <c r="Z76" s="543"/>
       <c r="AA76" s="436"/>
       <c r="AB76" s="87"/>
       <c r="AC76" s="96"/>
@@ -22747,20 +22771,20 @@
       <c r="HV76" s="6"/>
       <c r="HW76" s="6"/>
     </row>
-    <row r="77" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="537"/>
-      <c r="B77" s="537"/>
-      <c r="C77" s="537"/>
-      <c r="D77" s="537"/>
-      <c r="E77" s="612"/>
-      <c r="F77" s="580"/>
-      <c r="G77" s="602" t="s">
-        <v>27</v>
+    <row r="77" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A77" s="544"/>
+      <c r="B77" s="544"/>
+      <c r="C77" s="544"/>
+      <c r="D77" s="544"/>
+      <c r="E77" s="614"/>
+      <c r="F77" s="604"/>
+      <c r="G77" s="561" t="s">
+        <v>25</v>
       </c>
       <c r="H77" s="225"/>
       <c r="I77" s="6"/>
-      <c r="J77" s="599"/>
-      <c r="K77" s="539"/>
+      <c r="J77" s="605"/>
+      <c r="K77" s="541"/>
       <c r="L77" s="6"/>
       <c r="M77" s="142"/>
       <c r="N77" s="437"/>
@@ -22982,14 +23006,14 @@
       <c r="HV77" s="6"/>
       <c r="HW77" s="6"/>
     </row>
-    <row r="78" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="535"/>
-      <c r="B78" s="535"/>
-      <c r="C78" s="535"/>
-      <c r="D78" s="535"/>
-      <c r="E78" s="535"/>
-      <c r="F78" s="580"/>
-      <c r="G78" s="543"/>
+    <row r="78" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A78" s="538"/>
+      <c r="B78" s="538"/>
+      <c r="C78" s="538"/>
+      <c r="D78" s="538"/>
+      <c r="E78" s="538"/>
+      <c r="F78" s="604"/>
+      <c r="G78" s="552"/>
       <c r="H78" s="169"/>
       <c r="I78" s="26"/>
       <c r="J78" s="43"/>
@@ -23215,18 +23239,18 @@
       <c r="HV78" s="6"/>
       <c r="HW78" s="6"/>
     </row>
-    <row r="79" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A79" s="536"/>
-      <c r="B79" s="536"/>
-      <c r="C79" s="536"/>
-      <c r="D79" s="536"/>
-      <c r="E79" s="536"/>
-      <c r="F79" s="581"/>
-      <c r="G79" s="564"/>
+    <row r="79" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A79" s="539"/>
+      <c r="B79" s="539"/>
+      <c r="C79" s="539"/>
+      <c r="D79" s="539"/>
+      <c r="E79" s="539"/>
+      <c r="F79" s="641"/>
+      <c r="G79" s="562"/>
       <c r="H79" s="169"/>
       <c r="I79" s="26"/>
-      <c r="J79" s="637"/>
-      <c r="K79" s="566"/>
+      <c r="J79" s="596"/>
+      <c r="K79" s="568"/>
       <c r="L79" s="203"/>
       <c r="M79" s="203"/>
       <c r="N79" s="346"/>
@@ -23448,16 +23472,16 @@
       <c r="HV79" s="6"/>
       <c r="HW79" s="6"/>
     </row>
-    <row r="80" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A80" s="537"/>
-      <c r="B80" s="554"/>
-      <c r="C80" s="554"/>
-      <c r="D80" s="554"/>
-      <c r="E80" s="554"/>
-      <c r="F80" s="584" t="s">
-        <v>33</v>
+    <row r="80" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="544"/>
+      <c r="B80" s="557"/>
+      <c r="C80" s="557"/>
+      <c r="D80" s="557"/>
+      <c r="E80" s="557"/>
+      <c r="F80" s="643" t="s">
+        <v>29</v>
       </c>
-      <c r="G80" s="645" t="s">
+      <c r="G80" s="569" t="s">
         <v>18</v>
       </c>
       <c r="H80" s="235"/>
@@ -23685,14 +23709,14 @@
       <c r="HV80" s="6"/>
       <c r="HW80" s="6"/>
     </row>
-    <row r="81" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A81" s="535"/>
-      <c r="B81" s="535"/>
-      <c r="C81" s="535"/>
-      <c r="D81" s="535"/>
-      <c r="E81" s="535"/>
-      <c r="F81" s="580"/>
-      <c r="G81" s="543"/>
+    <row r="81" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="538"/>
+      <c r="B81" s="538"/>
+      <c r="C81" s="538"/>
+      <c r="D81" s="538"/>
+      <c r="E81" s="538"/>
+      <c r="F81" s="604"/>
+      <c r="G81" s="552"/>
       <c r="H81" s="169"/>
       <c r="I81" s="26"/>
       <c r="J81" s="26"/>
@@ -23918,14 +23942,14 @@
       <c r="HV81" s="6"/>
       <c r="HW81" s="6"/>
     </row>
-    <row r="82" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="536"/>
-      <c r="B82" s="536"/>
-      <c r="C82" s="536"/>
-      <c r="D82" s="536"/>
-      <c r="E82" s="536"/>
-      <c r="F82" s="580"/>
-      <c r="G82" s="544"/>
+    <row r="82" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A82" s="539"/>
+      <c r="B82" s="539"/>
+      <c r="C82" s="539"/>
+      <c r="D82" s="539"/>
+      <c r="E82" s="539"/>
+      <c r="F82" s="604"/>
+      <c r="G82" s="566"/>
       <c r="H82" s="169"/>
       <c r="I82" s="26"/>
       <c r="J82" s="26"/>
@@ -24151,24 +24175,24 @@
       <c r="HV82" s="6"/>
       <c r="HW82" s="6"/>
     </row>
-    <row r="83" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="534">
+    <row r="83" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A83" s="563">
         <v>10</v>
       </c>
-      <c r="B83" s="534">
+      <c r="B83" s="563">
         <v>10</v>
       </c>
-      <c r="C83" s="534">
+      <c r="C83" s="563">
         <v>7</v>
       </c>
-      <c r="D83" s="642">
+      <c r="D83" s="575">
         <v>5</v>
       </c>
-      <c r="E83" s="534">
+      <c r="E83" s="563">
         <v>2</v>
       </c>
-      <c r="F83" s="580"/>
-      <c r="G83" s="572" t="s">
+      <c r="F83" s="604"/>
+      <c r="G83" s="565" t="s">
         <v>19</v>
       </c>
       <c r="H83" s="358"/>
@@ -24179,10 +24203,10 @@
       <c r="M83" s="56"/>
       <c r="N83" s="56"/>
       <c r="O83" s="457"/>
-      <c r="P83" s="646"/>
-      <c r="Q83" s="586"/>
-      <c r="R83" s="586"/>
-      <c r="S83" s="617"/>
+      <c r="P83" s="570"/>
+      <c r="Q83" s="571"/>
+      <c r="R83" s="571"/>
+      <c r="S83" s="572"/>
       <c r="T83" s="458"/>
       <c r="U83" s="458"/>
       <c r="V83" s="458"/>
@@ -24396,14 +24420,14 @@
       <c r="HV83" s="6"/>
       <c r="HW83" s="6"/>
     </row>
-    <row r="84" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="535"/>
-      <c r="B84" s="535"/>
-      <c r="C84" s="535"/>
-      <c r="D84" s="535"/>
-      <c r="E84" s="535"/>
-      <c r="F84" s="580"/>
-      <c r="G84" s="543"/>
+    <row r="84" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A84" s="538"/>
+      <c r="B84" s="538"/>
+      <c r="C84" s="538"/>
+      <c r="D84" s="538"/>
+      <c r="E84" s="538"/>
+      <c r="F84" s="604"/>
+      <c r="G84" s="552"/>
       <c r="H84" s="169"/>
       <c r="I84" s="26"/>
       <c r="J84" s="26"/>
@@ -24629,14 +24653,14 @@
       <c r="HV84" s="6"/>
       <c r="HW84" s="6"/>
     </row>
-    <row r="85" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="536"/>
-      <c r="B85" s="536"/>
-      <c r="C85" s="536"/>
-      <c r="D85" s="536"/>
-      <c r="E85" s="536"/>
-      <c r="F85" s="580"/>
-      <c r="G85" s="544"/>
+    <row r="85" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A85" s="539"/>
+      <c r="B85" s="539"/>
+      <c r="C85" s="539"/>
+      <c r="D85" s="539"/>
+      <c r="E85" s="539"/>
+      <c r="F85" s="604"/>
+      <c r="G85" s="566"/>
       <c r="H85" s="169"/>
       <c r="I85" s="26"/>
       <c r="J85" s="26"/>
@@ -24862,36 +24886,36 @@
       <c r="HV85" s="6"/>
       <c r="HW85" s="6"/>
     </row>
-    <row r="86" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A86" s="534">
+    <row r="86" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="563">
         <v>24</v>
       </c>
-      <c r="B86" s="534">
+      <c r="B86" s="563">
         <v>24</v>
       </c>
-      <c r="C86" s="534">
+      <c r="C86" s="563">
         <v>21</v>
       </c>
-      <c r="D86" s="642">
+      <c r="D86" s="575">
         <v>19</v>
       </c>
-      <c r="E86" s="552"/>
-      <c r="F86" s="580"/>
-      <c r="G86" s="631" t="s">
+      <c r="E86" s="537"/>
+      <c r="F86" s="604"/>
+      <c r="G86" s="594" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="356"/>
       <c r="I86" s="37"/>
       <c r="J86" s="37"/>
       <c r="K86" s="357"/>
-      <c r="L86" s="557"/>
-      <c r="M86" s="546"/>
-      <c r="N86" s="546"/>
-      <c r="O86" s="546"/>
-      <c r="P86" s="546"/>
-      <c r="Q86" s="546"/>
-      <c r="R86" s="546"/>
-      <c r="S86" s="547"/>
+      <c r="L86" s="584"/>
+      <c r="M86" s="549"/>
+      <c r="N86" s="549"/>
+      <c r="O86" s="549"/>
+      <c r="P86" s="549"/>
+      <c r="Q86" s="549"/>
+      <c r="R86" s="549"/>
+      <c r="S86" s="580"/>
       <c r="T86" s="57"/>
       <c r="U86" s="58"/>
       <c r="V86" s="58"/>
@@ -24900,10 +24924,10 @@
       <c r="Y86" s="58"/>
       <c r="Z86" s="58"/>
       <c r="AA86" s="58"/>
-      <c r="AB86" s="557"/>
-      <c r="AC86" s="546"/>
-      <c r="AD86" s="546"/>
-      <c r="AE86" s="547"/>
+      <c r="AB86" s="584"/>
+      <c r="AC86" s="549"/>
+      <c r="AD86" s="549"/>
+      <c r="AE86" s="580"/>
       <c r="AF86" s="57"/>
       <c r="AG86" s="58"/>
       <c r="AH86" s="58"/>
@@ -25105,26 +25129,26 @@
       <c r="HV86" s="6"/>
       <c r="HW86" s="6"/>
     </row>
-    <row r="87" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A87" s="535"/>
-      <c r="B87" s="535"/>
-      <c r="C87" s="535"/>
-      <c r="D87" s="535"/>
-      <c r="E87" s="535"/>
-      <c r="F87" s="580"/>
-      <c r="G87" s="543"/>
+    <row r="87" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A87" s="538"/>
+      <c r="B87" s="538"/>
+      <c r="C87" s="538"/>
+      <c r="D87" s="538"/>
+      <c r="E87" s="538"/>
+      <c r="F87" s="604"/>
+      <c r="G87" s="552"/>
       <c r="H87" s="154"/>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
       <c r="K87" s="147"/>
-      <c r="L87" s="604"/>
-      <c r="M87" s="551"/>
-      <c r="N87" s="551"/>
-      <c r="O87" s="551"/>
-      <c r="P87" s="551"/>
-      <c r="Q87" s="551"/>
-      <c r="R87" s="551"/>
-      <c r="S87" s="539"/>
+      <c r="L87" s="628"/>
+      <c r="M87" s="543"/>
+      <c r="N87" s="543"/>
+      <c r="O87" s="543"/>
+      <c r="P87" s="543"/>
+      <c r="Q87" s="543"/>
+      <c r="R87" s="543"/>
+      <c r="S87" s="541"/>
       <c r="T87" s="60"/>
       <c r="U87" s="61"/>
       <c r="V87" s="61"/>
@@ -25133,10 +25157,10 @@
       <c r="Y87" s="61"/>
       <c r="Z87" s="61"/>
       <c r="AA87" s="61"/>
-      <c r="AB87" s="592"/>
-      <c r="AC87" s="551"/>
-      <c r="AD87" s="551"/>
-      <c r="AE87" s="539"/>
+      <c r="AB87" s="555"/>
+      <c r="AC87" s="543"/>
+      <c r="AD87" s="543"/>
+      <c r="AE87" s="541"/>
       <c r="AF87" s="135"/>
       <c r="AG87" s="67"/>
       <c r="AH87" s="67"/>
@@ -25338,14 +25362,14 @@
       <c r="HV87" s="6"/>
       <c r="HW87" s="6"/>
     </row>
-    <row r="88" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="536"/>
-      <c r="B88" s="536"/>
-      <c r="C88" s="536"/>
-      <c r="D88" s="536"/>
-      <c r="E88" s="536"/>
-      <c r="F88" s="580"/>
-      <c r="G88" s="632"/>
+    <row r="88" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A88" s="539"/>
+      <c r="B88" s="539"/>
+      <c r="C88" s="539"/>
+      <c r="D88" s="539"/>
+      <c r="E88" s="539"/>
+      <c r="F88" s="604"/>
+      <c r="G88" s="553"/>
       <c r="H88" s="462"/>
       <c r="I88" s="463"/>
       <c r="J88" s="463"/>
@@ -25367,8 +25391,8 @@
       <c r="Z88" s="73"/>
       <c r="AA88" s="73"/>
       <c r="AB88" s="225"/>
-      <c r="AC88" s="600"/>
-      <c r="AD88" s="551"/>
+      <c r="AC88" s="542"/>
+      <c r="AD88" s="543"/>
       <c r="AE88" s="151"/>
       <c r="AF88" s="465"/>
       <c r="AG88" s="264"/>
@@ -25571,38 +25595,38 @@
       <c r="HV88" s="6"/>
       <c r="HW88" s="6"/>
     </row>
-    <row r="89" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="552">
+    <row r="89" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A89" s="537">
         <v>0</v>
       </c>
-      <c r="B89" s="552">
+      <c r="B89" s="537">
         <v>0</v>
       </c>
-      <c r="C89" s="552">
+      <c r="C89" s="537">
         <v>0</v>
       </c>
-      <c r="D89" s="552">
+      <c r="D89" s="537">
         <v>0</v>
       </c>
-      <c r="E89" s="552">
+      <c r="E89" s="537">
         <v>0</v>
       </c>
-      <c r="F89" s="580"/>
-      <c r="G89" s="626" t="s">
-        <v>23</v>
+      <c r="F89" s="604"/>
+      <c r="G89" s="597" t="s">
+        <v>22</v>
       </c>
       <c r="H89" s="265"/>
       <c r="I89" s="54"/>
       <c r="J89" s="54"/>
       <c r="K89" s="266"/>
-      <c r="L89" s="570"/>
-      <c r="M89" s="551"/>
-      <c r="N89" s="551"/>
-      <c r="O89" s="551"/>
-      <c r="P89" s="551"/>
-      <c r="Q89" s="551"/>
-      <c r="R89" s="551"/>
-      <c r="S89" s="539"/>
+      <c r="L89" s="592"/>
+      <c r="M89" s="543"/>
+      <c r="N89" s="543"/>
+      <c r="O89" s="543"/>
+      <c r="P89" s="543"/>
+      <c r="Q89" s="543"/>
+      <c r="R89" s="543"/>
+      <c r="S89" s="541"/>
       <c r="T89" s="369"/>
       <c r="U89" s="370"/>
       <c r="V89" s="79"/>
@@ -25816,26 +25840,26 @@
       <c r="HV89" s="6"/>
       <c r="HW89" s="6"/>
     </row>
-    <row r="90" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="535"/>
-      <c r="B90" s="535"/>
-      <c r="C90" s="535"/>
-      <c r="D90" s="535"/>
-      <c r="E90" s="535"/>
-      <c r="F90" s="580"/>
-      <c r="G90" s="543"/>
+    <row r="90" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A90" s="538"/>
+      <c r="B90" s="538"/>
+      <c r="C90" s="538"/>
+      <c r="D90" s="538"/>
+      <c r="E90" s="538"/>
+      <c r="F90" s="604"/>
+      <c r="G90" s="552"/>
       <c r="H90" s="265"/>
       <c r="I90" s="54"/>
       <c r="J90" s="54"/>
       <c r="K90" s="263"/>
-      <c r="L90" s="543"/>
-      <c r="M90" s="551"/>
-      <c r="N90" s="551"/>
-      <c r="O90" s="551"/>
-      <c r="P90" s="551"/>
-      <c r="Q90" s="551"/>
-      <c r="R90" s="551"/>
-      <c r="S90" s="539"/>
+      <c r="L90" s="552"/>
+      <c r="M90" s="543"/>
+      <c r="N90" s="543"/>
+      <c r="O90" s="543"/>
+      <c r="P90" s="543"/>
+      <c r="Q90" s="543"/>
+      <c r="R90" s="543"/>
+      <c r="S90" s="541"/>
       <c r="T90" s="213"/>
       <c r="U90" s="84"/>
       <c r="V90" s="26"/>
@@ -26049,14 +26073,14 @@
       <c r="HV90" s="6"/>
       <c r="HW90" s="6"/>
     </row>
-    <row r="91" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="536"/>
-      <c r="B91" s="536"/>
-      <c r="C91" s="536"/>
-      <c r="D91" s="536"/>
-      <c r="E91" s="536"/>
-      <c r="F91" s="580"/>
-      <c r="G91" s="543"/>
+    <row r="91" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A91" s="539"/>
+      <c r="B91" s="539"/>
+      <c r="C91" s="539"/>
+      <c r="D91" s="539"/>
+      <c r="E91" s="539"/>
+      <c r="F91" s="604"/>
+      <c r="G91" s="552"/>
       <c r="H91" s="262"/>
       <c r="I91" s="70"/>
       <c r="J91" s="70"/>
@@ -26282,15 +26306,15 @@
       <c r="HV91" s="6"/>
       <c r="HW91" s="6"/>
     </row>
-    <row r="92" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A92" s="537"/>
-      <c r="B92" s="537"/>
-      <c r="C92" s="537"/>
-      <c r="D92" s="537"/>
-      <c r="E92" s="537"/>
-      <c r="F92" s="580"/>
-      <c r="G92" s="572" t="s">
-        <v>25</v>
+    <row r="92" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A92" s="544"/>
+      <c r="B92" s="544"/>
+      <c r="C92" s="544"/>
+      <c r="D92" s="544"/>
+      <c r="E92" s="544"/>
+      <c r="F92" s="604"/>
+      <c r="G92" s="565" t="s">
+        <v>24</v>
       </c>
       <c r="H92" s="258"/>
       <c r="I92" s="58"/>
@@ -26517,14 +26541,14 @@
       <c r="HV92" s="6"/>
       <c r="HW92" s="6"/>
     </row>
-    <row r="93" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="535"/>
-      <c r="B93" s="535"/>
-      <c r="C93" s="535"/>
-      <c r="D93" s="535"/>
-      <c r="E93" s="535"/>
-      <c r="F93" s="580"/>
-      <c r="G93" s="543"/>
+    <row r="93" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A93" s="538"/>
+      <c r="B93" s="538"/>
+      <c r="C93" s="538"/>
+      <c r="D93" s="538"/>
+      <c r="E93" s="538"/>
+      <c r="F93" s="604"/>
+      <c r="G93" s="552"/>
       <c r="H93" s="260"/>
       <c r="I93" s="67"/>
       <c r="J93" s="67"/>
@@ -26750,14 +26774,14 @@
       <c r="HV93" s="6"/>
       <c r="HW93" s="6"/>
     </row>
-    <row r="94" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="536"/>
-      <c r="B94" s="536"/>
-      <c r="C94" s="536"/>
-      <c r="D94" s="536"/>
-      <c r="E94" s="536"/>
-      <c r="F94" s="580"/>
-      <c r="G94" s="544"/>
+    <row r="94" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A94" s="539"/>
+      <c r="B94" s="539"/>
+      <c r="C94" s="539"/>
+      <c r="D94" s="539"/>
+      <c r="E94" s="539"/>
+      <c r="F94" s="604"/>
+      <c r="G94" s="566"/>
       <c r="H94" s="267"/>
       <c r="I94" s="94"/>
       <c r="J94" s="94"/>
@@ -26983,15 +27007,15 @@
       <c r="HV94" s="6"/>
       <c r="HW94" s="6"/>
     </row>
-    <row r="95" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="537"/>
-      <c r="B95" s="537"/>
-      <c r="C95" s="537"/>
-      <c r="D95" s="537"/>
-      <c r="E95" s="537"/>
-      <c r="F95" s="580"/>
-      <c r="G95" s="602" t="s">
-        <v>27</v>
+    <row r="95" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A95" s="544"/>
+      <c r="B95" s="544"/>
+      <c r="C95" s="544"/>
+      <c r="D95" s="544"/>
+      <c r="E95" s="544"/>
+      <c r="F95" s="604"/>
+      <c r="G95" s="561" t="s">
+        <v>25</v>
       </c>
       <c r="H95" s="169"/>
       <c r="I95" s="26"/>
@@ -27218,14 +27242,14 @@
       <c r="HV95" s="6"/>
       <c r="HW95" s="6"/>
     </row>
-    <row r="96" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="535"/>
-      <c r="B96" s="535"/>
-      <c r="C96" s="535"/>
-      <c r="D96" s="535"/>
-      <c r="E96" s="535"/>
-      <c r="F96" s="580"/>
-      <c r="G96" s="543"/>
+    <row r="96" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A96" s="538"/>
+      <c r="B96" s="538"/>
+      <c r="C96" s="538"/>
+      <c r="D96" s="538"/>
+      <c r="E96" s="538"/>
+      <c r="F96" s="604"/>
+      <c r="G96" s="552"/>
       <c r="H96" s="169"/>
       <c r="I96" s="26"/>
       <c r="J96" s="26"/>
@@ -27451,14 +27475,14 @@
       <c r="HV96" s="6"/>
       <c r="HW96" s="6"/>
     </row>
-    <row r="97" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="536"/>
-      <c r="B97" s="536"/>
-      <c r="C97" s="536"/>
-      <c r="D97" s="536"/>
-      <c r="E97" s="536"/>
-      <c r="F97" s="581"/>
-      <c r="G97" s="564"/>
+    <row r="97" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A97" s="539"/>
+      <c r="B97" s="539"/>
+      <c r="C97" s="539"/>
+      <c r="D97" s="539"/>
+      <c r="E97" s="539"/>
+      <c r="F97" s="641"/>
+      <c r="G97" s="562"/>
       <c r="H97" s="169"/>
       <c r="I97" s="26"/>
       <c r="J97" s="26"/>
@@ -27684,16 +27708,16 @@
       <c r="HV97" s="6"/>
       <c r="HW97" s="6"/>
     </row>
-    <row r="98" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A98" s="537"/>
-      <c r="B98" s="537"/>
-      <c r="C98" s="537"/>
-      <c r="D98" s="537"/>
-      <c r="E98" s="537"/>
-      <c r="F98" s="597" t="s">
-        <v>34</v>
+    <row r="98" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A98" s="544"/>
+      <c r="B98" s="544"/>
+      <c r="C98" s="544"/>
+      <c r="D98" s="544"/>
+      <c r="E98" s="544"/>
+      <c r="F98" s="603" t="s">
+        <v>30</v>
       </c>
-      <c r="G98" s="596" t="s">
+      <c r="G98" s="637" t="s">
         <v>18</v>
       </c>
       <c r="H98" s="481"/>
@@ -27921,14 +27945,14 @@
       <c r="HV98" s="6"/>
       <c r="HW98" s="6"/>
     </row>
-    <row r="99" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A99" s="535"/>
-      <c r="B99" s="535"/>
-      <c r="C99" s="535"/>
-      <c r="D99" s="535"/>
-      <c r="E99" s="535"/>
-      <c r="F99" s="580"/>
-      <c r="G99" s="543"/>
+    <row r="99" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="538"/>
+      <c r="B99" s="538"/>
+      <c r="C99" s="538"/>
+      <c r="D99" s="538"/>
+      <c r="E99" s="538"/>
+      <c r="F99" s="604"/>
+      <c r="G99" s="552"/>
       <c r="H99" s="225"/>
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
@@ -28154,14 +28178,14 @@
       <c r="HV99" s="6"/>
       <c r="HW99" s="6"/>
     </row>
-    <row r="100" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="536"/>
-      <c r="B100" s="536"/>
-      <c r="C100" s="536"/>
-      <c r="D100" s="536"/>
-      <c r="E100" s="536"/>
-      <c r="F100" s="580"/>
-      <c r="G100" s="543"/>
+    <row r="100" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A100" s="539"/>
+      <c r="B100" s="539"/>
+      <c r="C100" s="539"/>
+      <c r="D100" s="539"/>
+      <c r="E100" s="539"/>
+      <c r="F100" s="604"/>
+      <c r="G100" s="552"/>
       <c r="H100" s="225"/>
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
@@ -28387,22 +28411,22 @@
       <c r="HV100" s="6"/>
       <c r="HW100" s="6"/>
     </row>
-    <row r="101" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A101" s="534">
+    <row r="101" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="563">
         <v>11</v>
       </c>
-      <c r="B101" s="534">
+      <c r="B101" s="563">
         <v>11</v>
       </c>
-      <c r="C101" s="534">
+      <c r="C101" s="563">
         <v>8</v>
       </c>
-      <c r="D101" s="534">
+      <c r="D101" s="563">
         <v>6</v>
       </c>
-      <c r="E101" s="552"/>
-      <c r="F101" s="580"/>
-      <c r="G101" s="572" t="s">
+      <c r="E101" s="537"/>
+      <c r="F101" s="604"/>
+      <c r="G101" s="565" t="s">
         <v>19</v>
       </c>
       <c r="H101" s="356"/>
@@ -28630,14 +28654,14 @@
       <c r="HV101" s="6"/>
       <c r="HW101" s="6"/>
     </row>
-    <row r="102" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A102" s="535"/>
-      <c r="B102" s="535"/>
-      <c r="C102" s="535"/>
-      <c r="D102" s="535"/>
-      <c r="E102" s="535"/>
-      <c r="F102" s="580"/>
-      <c r="G102" s="543"/>
+    <row r="102" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A102" s="538"/>
+      <c r="B102" s="538"/>
+      <c r="C102" s="538"/>
+      <c r="D102" s="538"/>
+      <c r="E102" s="538"/>
+      <c r="F102" s="604"/>
+      <c r="G102" s="552"/>
       <c r="H102" s="154"/>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
@@ -28863,14 +28887,14 @@
       <c r="HV102" s="6"/>
       <c r="HW102" s="6"/>
     </row>
-    <row r="103" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="536"/>
-      <c r="B103" s="536"/>
-      <c r="C103" s="536"/>
-      <c r="D103" s="536"/>
-      <c r="E103" s="536"/>
-      <c r="F103" s="580"/>
-      <c r="G103" s="544"/>
+    <row r="103" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A103" s="539"/>
+      <c r="B103" s="539"/>
+      <c r="C103" s="539"/>
+      <c r="D103" s="539"/>
+      <c r="E103" s="539"/>
+      <c r="F103" s="604"/>
+      <c r="G103" s="566"/>
       <c r="H103" s="488"/>
       <c r="I103" s="47"/>
       <c r="J103" s="47"/>
@@ -29096,24 +29120,24 @@
       <c r="HV103" s="6"/>
       <c r="HW103" s="6"/>
     </row>
-    <row r="104" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A104" s="534">
+    <row r="104" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="563">
         <v>25</v>
       </c>
-      <c r="B104" s="534">
+      <c r="B104" s="563">
         <v>25</v>
       </c>
-      <c r="C104" s="534">
+      <c r="C104" s="563">
         <v>22</v>
       </c>
-      <c r="D104" s="534">
+      <c r="D104" s="563">
         <v>20</v>
       </c>
-      <c r="E104" s="552">
+      <c r="E104" s="537">
         <v>0</v>
       </c>
-      <c r="F104" s="580"/>
-      <c r="G104" s="587" t="s">
+      <c r="F104" s="604"/>
+      <c r="G104" s="601" t="s">
         <v>20</v>
       </c>
       <c r="H104" s="356"/>
@@ -29341,14 +29365,14 @@
       <c r="HV104" s="6"/>
       <c r="HW104" s="6"/>
     </row>
-    <row r="105" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A105" s="535"/>
-      <c r="B105" s="535"/>
-      <c r="C105" s="535"/>
-      <c r="D105" s="535"/>
-      <c r="E105" s="535"/>
-      <c r="F105" s="580"/>
-      <c r="G105" s="543"/>
+    <row r="105" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="538"/>
+      <c r="B105" s="538"/>
+      <c r="C105" s="538"/>
+      <c r="D105" s="538"/>
+      <c r="E105" s="538"/>
+      <c r="F105" s="604"/>
+      <c r="G105" s="552"/>
       <c r="H105" s="154"/>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
@@ -29574,14 +29598,14 @@
       <c r="HV105" s="6"/>
       <c r="HW105" s="6"/>
     </row>
-    <row r="106" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="536"/>
-      <c r="B106" s="536"/>
-      <c r="C106" s="536"/>
-      <c r="D106" s="536"/>
-      <c r="E106" s="536"/>
-      <c r="F106" s="580"/>
-      <c r="G106" s="588"/>
+    <row r="106" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A106" s="539"/>
+      <c r="B106" s="539"/>
+      <c r="C106" s="539"/>
+      <c r="D106" s="539"/>
+      <c r="E106" s="539"/>
+      <c r="F106" s="604"/>
+      <c r="G106" s="602"/>
       <c r="H106" s="462"/>
       <c r="I106" s="463"/>
       <c r="J106" s="463"/>
@@ -29807,25 +29831,25 @@
       <c r="HV106" s="6"/>
       <c r="HW106" s="6"/>
     </row>
-    <row r="107" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="552">
+    <row r="107" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A107" s="537">
         <v>0</v>
       </c>
-      <c r="B107" s="552">
+      <c r="B107" s="537">
         <v>0</v>
       </c>
-      <c r="C107" s="552">
+      <c r="C107" s="537">
         <v>0</v>
       </c>
-      <c r="D107" s="552">
+      <c r="D107" s="537">
         <v>0</v>
       </c>
-      <c r="E107" s="552">
+      <c r="E107" s="537">
         <v>0</v>
       </c>
-      <c r="F107" s="580"/>
-      <c r="G107" s="589" t="s">
-        <v>23</v>
+      <c r="F107" s="604"/>
+      <c r="G107" s="587" t="s">
+        <v>22</v>
       </c>
       <c r="H107" s="154"/>
       <c r="I107" s="10"/>
@@ -30052,14 +30076,14 @@
       <c r="HV107" s="6"/>
       <c r="HW107" s="6"/>
     </row>
-    <row r="108" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A108" s="535"/>
-      <c r="B108" s="535"/>
-      <c r="C108" s="535"/>
-      <c r="D108" s="535"/>
-      <c r="E108" s="535"/>
-      <c r="F108" s="580"/>
-      <c r="G108" s="543"/>
+    <row r="108" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A108" s="538"/>
+      <c r="B108" s="538"/>
+      <c r="C108" s="538"/>
+      <c r="D108" s="538"/>
+      <c r="E108" s="538"/>
+      <c r="F108" s="604"/>
+      <c r="G108" s="552"/>
       <c r="H108" s="154"/>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
@@ -30285,14 +30309,14 @@
       <c r="HV108" s="6"/>
       <c r="HW108" s="6"/>
     </row>
-    <row r="109" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="536"/>
-      <c r="B109" s="536"/>
-      <c r="C109" s="536"/>
-      <c r="D109" s="536"/>
-      <c r="E109" s="536"/>
-      <c r="F109" s="580"/>
-      <c r="G109" s="544"/>
+    <row r="109" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A109" s="539"/>
+      <c r="B109" s="539"/>
+      <c r="C109" s="539"/>
+      <c r="D109" s="539"/>
+      <c r="E109" s="539"/>
+      <c r="F109" s="604"/>
+      <c r="G109" s="566"/>
       <c r="H109" s="154"/>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
@@ -30518,15 +30542,15 @@
       <c r="HV109" s="6"/>
       <c r="HW109" s="6"/>
     </row>
-    <row r="110" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A110" s="537"/>
-      <c r="B110" s="537"/>
-      <c r="C110" s="537"/>
-      <c r="D110" s="537"/>
-      <c r="E110" s="537"/>
-      <c r="F110" s="580"/>
-      <c r="G110" s="572" t="s">
-        <v>25</v>
+    <row r="110" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A110" s="544"/>
+      <c r="B110" s="544"/>
+      <c r="C110" s="544"/>
+      <c r="D110" s="544"/>
+      <c r="E110" s="544"/>
+      <c r="F110" s="604"/>
+      <c r="G110" s="565" t="s">
+        <v>24</v>
       </c>
       <c r="H110" s="498"/>
       <c r="I110" s="499"/>
@@ -30753,14 +30777,14 @@
       <c r="HV110" s="6"/>
       <c r="HW110" s="6"/>
     </row>
-    <row r="111" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" s="535"/>
-      <c r="B111" s="535"/>
-      <c r="C111" s="535"/>
-      <c r="D111" s="535"/>
-      <c r="E111" s="535"/>
-      <c r="F111" s="580"/>
-      <c r="G111" s="543"/>
+    <row r="111" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A111" s="538"/>
+      <c r="B111" s="538"/>
+      <c r="C111" s="538"/>
+      <c r="D111" s="538"/>
+      <c r="E111" s="538"/>
+      <c r="F111" s="604"/>
+      <c r="G111" s="552"/>
       <c r="H111" s="507"/>
       <c r="I111" s="508"/>
       <c r="J111" s="508"/>
@@ -30986,14 +31010,14 @@
       <c r="HV111" s="6"/>
       <c r="HW111" s="6"/>
     </row>
-    <row r="112" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="536"/>
-      <c r="B112" s="536"/>
-      <c r="C112" s="536"/>
-      <c r="D112" s="536"/>
-      <c r="E112" s="536"/>
-      <c r="F112" s="580"/>
-      <c r="G112" s="544"/>
+    <row r="112" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A112" s="539"/>
+      <c r="B112" s="539"/>
+      <c r="C112" s="539"/>
+      <c r="D112" s="539"/>
+      <c r="E112" s="539"/>
+      <c r="F112" s="604"/>
+      <c r="G112" s="566"/>
       <c r="H112" s="512"/>
       <c r="I112" s="513"/>
       <c r="J112" s="514"/>
@@ -31219,15 +31243,15 @@
       <c r="HV112" s="6"/>
       <c r="HW112" s="6"/>
     </row>
-    <row r="113" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="537"/>
-      <c r="B113" s="537"/>
-      <c r="C113" s="537"/>
-      <c r="D113" s="537"/>
-      <c r="E113" s="537"/>
-      <c r="F113" s="580"/>
-      <c r="G113" s="640" t="s">
-        <v>27</v>
+    <row r="113" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A113" s="544"/>
+      <c r="B113" s="544"/>
+      <c r="C113" s="544"/>
+      <c r="D113" s="544"/>
+      <c r="E113" s="544"/>
+      <c r="F113" s="604"/>
+      <c r="G113" s="616" t="s">
+        <v>25</v>
       </c>
       <c r="H113" s="507"/>
       <c r="I113" s="508"/>
@@ -31454,14 +31478,14 @@
       <c r="HV113" s="6"/>
       <c r="HW113" s="6"/>
     </row>
-    <row r="114" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="535"/>
-      <c r="B114" s="535"/>
-      <c r="C114" s="535"/>
-      <c r="D114" s="535"/>
-      <c r="E114" s="535"/>
-      <c r="F114" s="580"/>
-      <c r="G114" s="543"/>
+    <row r="114" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A114" s="538"/>
+      <c r="B114" s="538"/>
+      <c r="C114" s="538"/>
+      <c r="D114" s="538"/>
+      <c r="E114" s="538"/>
+      <c r="F114" s="604"/>
+      <c r="G114" s="552"/>
       <c r="H114" s="507"/>
       <c r="I114" s="508"/>
       <c r="J114" s="221"/>
@@ -31687,14 +31711,14 @@
       <c r="HV114" s="6"/>
       <c r="HW114" s="6"/>
     </row>
-    <row r="115" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="536"/>
-      <c r="B115" s="536"/>
-      <c r="C115" s="536"/>
-      <c r="D115" s="536"/>
-      <c r="E115" s="536"/>
-      <c r="F115" s="580"/>
-      <c r="G115" s="641"/>
+    <row r="115" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A115" s="539"/>
+      <c r="B115" s="539"/>
+      <c r="C115" s="539"/>
+      <c r="D115" s="539"/>
+      <c r="E115" s="539"/>
+      <c r="F115" s="604"/>
+      <c r="G115" s="617"/>
       <c r="H115" s="524"/>
       <c r="I115" s="525"/>
       <c r="J115" s="526"/>
@@ -31920,7 +31944,7 @@
       <c r="HV115" s="6"/>
       <c r="HW115" s="6"/>
     </row>
-    <row r="116" spans="1:231" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:231" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A116" s="530" t="s">
         <v>5</v>
       </c>
@@ -31938,48 +31962,48 @@
       </c>
       <c r="F116" s="531"/>
       <c r="G116" s="532"/>
-      <c r="H116" s="623" t="s">
+      <c r="H116" s="611" t="s">
         <v>10</v>
       </c>
-      <c r="I116" s="561"/>
-      <c r="J116" s="561"/>
-      <c r="K116" s="595"/>
-      <c r="L116" s="577" t="s">
+      <c r="I116" s="559"/>
+      <c r="J116" s="559"/>
+      <c r="K116" s="612"/>
+      <c r="L116" s="600" t="s">
         <v>11</v>
       </c>
-      <c r="M116" s="561"/>
-      <c r="N116" s="561"/>
-      <c r="O116" s="578"/>
-      <c r="P116" s="630" t="s">
+      <c r="M116" s="559"/>
+      <c r="N116" s="559"/>
+      <c r="O116" s="560"/>
+      <c r="P116" s="558" t="s">
         <v>12</v>
       </c>
-      <c r="Q116" s="561"/>
-      <c r="R116" s="561"/>
-      <c r="S116" s="578"/>
-      <c r="T116" s="636" t="s">
+      <c r="Q116" s="559"/>
+      <c r="R116" s="559"/>
+      <c r="S116" s="560"/>
+      <c r="T116" s="615" t="s">
         <v>13</v>
       </c>
-      <c r="U116" s="561"/>
-      <c r="V116" s="561"/>
-      <c r="W116" s="595"/>
-      <c r="X116" s="560" t="s">
+      <c r="U116" s="559"/>
+      <c r="V116" s="559"/>
+      <c r="W116" s="612"/>
+      <c r="X116" s="626" t="s">
         <v>14</v>
       </c>
-      <c r="Y116" s="561"/>
-      <c r="Z116" s="561"/>
-      <c r="AA116" s="561"/>
-      <c r="AB116" s="630" t="s">
+      <c r="Y116" s="559"/>
+      <c r="Z116" s="559"/>
+      <c r="AA116" s="559"/>
+      <c r="AB116" s="558" t="s">
         <v>15</v>
       </c>
-      <c r="AC116" s="561"/>
-      <c r="AD116" s="561"/>
-      <c r="AE116" s="578"/>
-      <c r="AF116" s="613" t="s">
+      <c r="AC116" s="559"/>
+      <c r="AD116" s="559"/>
+      <c r="AE116" s="560"/>
+      <c r="AF116" s="623" t="s">
         <v>16</v>
       </c>
-      <c r="AG116" s="561"/>
-      <c r="AH116" s="561"/>
-      <c r="AI116" s="614"/>
+      <c r="AG116" s="559"/>
+      <c r="AH116" s="559"/>
+      <c r="AI116" s="621"/>
       <c r="AJ116" s="6"/>
       <c r="AK116" s="6"/>
       <c r="AL116" s="6"/>
@@ -32177,9 +32201,9 @@
       <c r="HV116" s="6"/>
       <c r="HW116" s="6"/>
     </row>
-    <row r="117" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A117" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -32412,9 +32436,9 @@
       <c r="HV117" s="6"/>
       <c r="HW117" s="6"/>
     </row>
-    <row r="118" spans="1:231" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:231" ht="36.75" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A118" s="533" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -32422,7 +32446,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
@@ -32436,7 +32460,7 @@
       <c r="Q118" s="10"/>
       <c r="R118" s="10"/>
       <c r="S118" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="T118" s="10"/>
       <c r="U118" s="10"/>
@@ -32651,205 +32675,408 @@
       <c r="HV118" s="6"/>
       <c r="HW118" s="6"/>
     </row>
-    <row r="119" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="120" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="121" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="122" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="123" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="124" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="125" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="126" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="127" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="128" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="129" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="130" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="131" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="132" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="133" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="134" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="135" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="136" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="137" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="138" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="139" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="140" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="141" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="142" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="143" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="144" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="145" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="146" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="148" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="149" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="150" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="151" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="152" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="153" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="154" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="155" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="156" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="157" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="158" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="159" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="160" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="161" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="162" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="163" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="164" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="165" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="166" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="167" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="168" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="169" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="170" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="171" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="172" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="173" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="174" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="175" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="176" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="177" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="178" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="179" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="180" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="181" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="182" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="183" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="184" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="185" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="186" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="187" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="188" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="189" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="190" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="191" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="192" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="193" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="194" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="195" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="196" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="197" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="198" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="199" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="200" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="201" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="202" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="203" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="204" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="205" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="206" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="207" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="208" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="209" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="210" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="211" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="212" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="213" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="214" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="215" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="216" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="217" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="218" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="219" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="220" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="221" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="222" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="223" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="224" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="225" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="226" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="227" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="228" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="229" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="230" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="231" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="232" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="233" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="234" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="235" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="236" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="237" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="238" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="239" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="240" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="119" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="120" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="121" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="122" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="123" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="124" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="125" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="126" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="127" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="128" spans="1:231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="129" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="130" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="131" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="132" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="133" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="134" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="135" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="136" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="137" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="138" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="139" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="140" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="141" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="142" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="143" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="144" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="145" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="146" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="148" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="149" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="150" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="151" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="152" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="153" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="154" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="155" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="156" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="157" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="159" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="160" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="161" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="162" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="163" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="164" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="165" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="166" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="167" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="168" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="170" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="171" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="172" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="173" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="174" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="175" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="176" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="177" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="178" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="179" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="180" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="181" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="182" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="183" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="184" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="185" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="186" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="187" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="188" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="189" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="190" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="191" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="192" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="193" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="194" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="195" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="196" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="197" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="198" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="199" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="200" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="201" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="202" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="203" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="204" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="205" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="206" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="207" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="208" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="209" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="210" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="211" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="212" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="213" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="214" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="215" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="216" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="217" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="218" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="219" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="220" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="221" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="222" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="223" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="224" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="225" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="227" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="228" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="229" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="230" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="231" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="232" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="233" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="234" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="235" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="236" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="237" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="238" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="239" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="240" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="349">
-    <mergeCell ref="AB68:AE68"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="Y76:Z76"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="Y40:Z40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="L71:O71"/>
-    <mergeCell ref="AB65:AE65"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="G95:G97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="AB41:AE41"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="E65:E67"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="P83:S83"/>
-    <mergeCell ref="E86:E88"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="AB53:AE53"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="X14:AA14"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="E83:E85"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="X74:AA74"/>
+    <mergeCell ref="D71:D73"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="F80:F97"/>
+    <mergeCell ref="AG51:AH51"/>
+    <mergeCell ref="AF50:AI50"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="D110:D112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="E113:E115"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="E107:E109"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="D113:D115"/>
+    <mergeCell ref="D98:D100"/>
+    <mergeCell ref="D101:D103"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="L116:O116"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="AF53:AI53"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="AB86:AE86"/>
+    <mergeCell ref="AF71:AI71"/>
+    <mergeCell ref="E101:E103"/>
+    <mergeCell ref="E95:E97"/>
+    <mergeCell ref="G101:G103"/>
+    <mergeCell ref="X38:AA38"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="F62:F79"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="AC88:AD88"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="AB87:AE87"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="E104:E106"/>
+    <mergeCell ref="X75:AA75"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="G98:G100"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="E74:E76"/>
+    <mergeCell ref="T74:W74"/>
+    <mergeCell ref="L89:S90"/>
+    <mergeCell ref="F26:F43"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="F44:F61"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="AF116:AI116"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="AF1:AI1"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="X116:AA116"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="E59:E61"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="G107:G109"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="L86:S87"/>
+    <mergeCell ref="U76:V76"/>
+    <mergeCell ref="AF38:AI38"/>
+    <mergeCell ref="AF6:AI6"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="AB71:AE71"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="F8:F25"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="AF35:AI35"/>
+    <mergeCell ref="X6:AA6"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="H116:K116"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="AB74:AE74"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="G77:G79"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="X39:AA39"/>
+    <mergeCell ref="P116:S116"/>
+    <mergeCell ref="AB56:AE56"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="T116:W116"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="AB116:AE116"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="P6:S6"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="T75:W75"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="E98:E100"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="G68:G70"/>
+    <mergeCell ref="F98:F115"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="H71:K71"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="G59:G61"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="AF68:AI68"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="L74:S75"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="G86:G88"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="E89:E91"/>
+    <mergeCell ref="G89:G91"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="P71:S71"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="A101:A103"/>
     <mergeCell ref="G8:G10"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="AB38:AE38"/>
@@ -32874,6 +33101,17 @@
     <mergeCell ref="AB14:AE14"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="E20:E22"/>
+    <mergeCell ref="X14:AA14"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="E83:E85"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="G23:G25"/>
     <mergeCell ref="C56:C58"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="B11:B13"/>
@@ -32881,271 +33119,57 @@
     <mergeCell ref="R40:S40"/>
     <mergeCell ref="B38:B40"/>
     <mergeCell ref="D38:D40"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="AF68:AI68"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="L74:S75"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="G86:G88"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="E89:E91"/>
-    <mergeCell ref="G89:G91"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="P71:S71"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="G59:G61"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="P6:S6"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="T75:W75"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="C98:C100"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="E98:E100"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="G68:G70"/>
-    <mergeCell ref="F98:F115"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="H71:K71"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="H116:K116"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="AB74:AE74"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="X39:AA39"/>
-    <mergeCell ref="P116:S116"/>
-    <mergeCell ref="AB56:AE56"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="T116:W116"/>
-    <mergeCell ref="G113:G115"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="AB116:AE116"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="E110:E112"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="G95:G97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="E65:E67"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="P83:S83"/>
+    <mergeCell ref="E86:E88"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="AB68:AE68"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="Y76:Z76"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="Y40:Z40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="L71:O71"/>
+    <mergeCell ref="AB65:AE65"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="AB41:AE41"/>
+    <mergeCell ref="AB53:AE53"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="A77:A79"/>
     <mergeCell ref="A95:A97"/>
     <mergeCell ref="C101:C103"/>
     <mergeCell ref="C95:C97"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="AF38:AI38"/>
-    <mergeCell ref="AF6:AI6"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="AB71:AE71"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="AF116:AI116"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="AF1:AI1"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="X116:AA116"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="E59:E61"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="G107:G109"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="E56:E58"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="L86:S87"/>
-    <mergeCell ref="U76:V76"/>
-    <mergeCell ref="C8:C10"/>
     <mergeCell ref="B107:B109"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="P17:Q17"/>
     <mergeCell ref="D95:D97"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="F8:F25"/>
-    <mergeCell ref="C29:C31"/>
     <mergeCell ref="C89:C91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="F44:F61"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="AC88:AD88"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="AB87:AE87"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="E104:E106"/>
-    <mergeCell ref="X75:AA75"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="G98:G100"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="E74:E76"/>
-    <mergeCell ref="T74:W74"/>
-    <mergeCell ref="L89:S90"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F26:F43"/>
-    <mergeCell ref="AF35:AI35"/>
-    <mergeCell ref="L116:O116"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="AF53:AI53"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="AB86:AE86"/>
-    <mergeCell ref="AF71:AI71"/>
-    <mergeCell ref="E101:E103"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="G101:G103"/>
-    <mergeCell ref="X38:AA38"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="F62:F79"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="X6:AA6"/>
-    <mergeCell ref="B83:B85"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="D101:D103"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="D110:D112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="E113:E115"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="E107:E109"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="X74:AA74"/>
-    <mergeCell ref="D71:D73"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="F80:F97"/>
-    <mergeCell ref="AG51:AH51"/>
-    <mergeCell ref="AF50:AI50"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D113:D115"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="D98:D100"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
